--- a/results.xlsx
+++ b/results.xlsx
@@ -5,22 +5,20 @@
   <sheets>
     <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Sheet1!$A$13:$F$33</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="vVrblPq3u9j6GelkeDjOy09TbW4/wVg+xU3NS03keaE="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="9/jUrh7nvB2edeN/pbrzDAS+gzkAXuqdV/eXyrMK0nY="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="49">
-  <si>
-    <t>Updated as on June 19, 2026</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="57">
+  <si>
+    <t>Updated as on June 20, 2026</t>
   </si>
   <si>
     <t>Player</t>
@@ -65,6 +63,9 @@
     <t>Match</t>
   </si>
   <si>
+    <t>Date</t>
+  </si>
+  <si>
     <t>Prediction</t>
   </si>
   <si>
@@ -161,16 +162,40 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Czechia vs South Africa</t>
-  </si>
-  <si>
-    <t>Czechia</t>
+    <t>USA vs Australia</t>
+  </si>
+  <si>
+    <t>Türkiye vs Paraguay</t>
+  </si>
+  <si>
+    <t>Türkiye</t>
+  </si>
+  <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
+    <t>Brazil vs Haiti</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Scotland vs Morocco</t>
+  </si>
+  <si>
+    <t>Morocco</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="d mmmm"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <sz val="10.0"/>
@@ -275,7 +300,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -284,10 +309,10 @@
     </xf>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -297,7 +322,7 @@
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -308,10 +333,16 @@
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -533,12 +564,12 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.0"/>
-    <col customWidth="1" min="2" max="2" width="5.38"/>
-    <col customWidth="1" min="3" max="3" width="6.5"/>
-    <col customWidth="1" min="4" max="4" width="6.38"/>
-    <col customWidth="1" min="5" max="5" width="6.5"/>
-    <col customWidth="1" min="6" max="6" width="4.63"/>
+    <col customWidth="1" min="1" max="1" width="14.75"/>
+    <col customWidth="1" min="2" max="3" width="5.38"/>
+    <col customWidth="1" min="4" max="4" width="6.5"/>
+    <col customWidth="1" min="5" max="5" width="6.38"/>
+    <col customWidth="1" min="6" max="6" width="6.5"/>
+    <col customWidth="1" min="7" max="7" width="4.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -547,180 +578,167 @@
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="3"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="3"/>
+      <c r="E2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="F2" s="3"/>
+      <c r="G2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="7">
-        <v>230.0</v>
-      </c>
       <c r="C3" s="7">
+        <v>130.0</v>
+      </c>
+      <c r="E3" s="7">
         <v>0.0</v>
       </c>
-      <c r="D3" s="7">
-        <f t="shared" ref="D3:D10" si="1">B3-C3</f>
-        <v>230</v>
-      </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="G3" s="7">
+        <f t="shared" ref="G3:G10" si="1">C3-E3</f>
+        <v>130</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="9">
-        <v>310.0</v>
-      </c>
       <c r="C4" s="9">
-        <v>20.0</v>
-      </c>
-      <c r="D4" s="9">
+        <v>380.0</v>
+      </c>
+      <c r="E4" s="9">
+        <v>220.0</v>
+      </c>
+      <c r="G4" s="9">
         <f t="shared" si="1"/>
-        <v>290</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+        <v>160</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="7">
-        <v>250.0</v>
-      </c>
       <c r="C5" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="D5" s="7">
+        <v>400.0</v>
+      </c>
+      <c r="E5" s="7">
+        <v>70.0</v>
+      </c>
+      <c r="G5" s="7">
         <f t="shared" si="1"/>
-        <v>250</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+        <v>330</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="9">
-        <v>400.0</v>
-      </c>
       <c r="C6" s="9">
-        <v>790.0</v>
-      </c>
-      <c r="D6" s="9">
+        <v>500.0</v>
+      </c>
+      <c r="E6" s="9">
+        <v>890.0</v>
+      </c>
+      <c r="G6" s="9">
         <f t="shared" si="1"/>
         <v>-390</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7">
-        <v>200.0</v>
-      </c>
       <c r="C7" s="7">
+        <v>400.0</v>
+      </c>
+      <c r="E7" s="7">
         <v>30.0</v>
       </c>
-      <c r="D7" s="7">
+      <c r="G7" s="7">
         <f t="shared" si="1"/>
-        <v>170</v>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+        <v>370</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="9">
+      <c r="C8" s="9">
         <v>250.0</v>
       </c>
-      <c r="C8" s="9">
+      <c r="E8" s="9">
         <v>50.0</v>
       </c>
-      <c r="D8" s="9">
+      <c r="G8" s="9">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="7">
+      <c r="C9" s="7">
         <v>330.0</v>
       </c>
-      <c r="C9" s="7">
+      <c r="E9" s="7">
         <v>200.0</v>
       </c>
-      <c r="D9" s="7">
+      <c r="G9" s="7">
         <f t="shared" si="1"/>
         <v>130</v>
       </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="9">
-        <v>250.0</v>
-      </c>
       <c r="C10" s="9">
-        <v>1130.0</v>
-      </c>
-      <c r="D10" s="9">
+        <v>350.0</v>
+      </c>
+      <c r="E10" s="9">
+        <v>1280.0</v>
+      </c>
+      <c r="G10" s="9">
         <f t="shared" si="1"/>
-        <v>-880</v>
-      </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
+        <v>-930</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="5">
-        <f t="shared" ref="B11:D11" si="2">SUM(B3:B10)</f>
-        <v>2220</v>
-      </c>
-      <c r="C11" s="5">
-        <f t="shared" si="2"/>
-        <v>2220</v>
-      </c>
-      <c r="D11" s="5">
-        <f t="shared" si="2"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="4">
+        <f>SUM(C3:C10)</f>
+        <v>2740</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="4">
+        <f>SUM(E3:F10)</f>
+        <v>2740</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="5">
+        <f>SUM(G3:G10)</f>
         <v>0</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
@@ -729,6 +747,7 @@
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="5" t="s">
@@ -749,403 +768,588 @@
       <c r="F13" s="5" t="s">
         <v>19</v>
       </c>
+      <c r="G13" s="5" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="11" t="s">
         <v>21</v>
       </c>
+      <c r="B14" s="12">
+        <v>46186.0</v>
+      </c>
       <c r="C14" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D14" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="F14" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="12">
+      <c r="G14" s="13">
         <v>230.0</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="13" t="s">
+      <c r="A15" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="13" t="s">
+      <c r="B15" s="15">
+        <v>46186.0</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="F15" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="14">
+      <c r="G15" s="16">
         <v>80.0</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="B16" s="12">
+        <v>46187.0</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D16" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="F16" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="12">
+      <c r="G16" s="13">
         <v>100.0</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="13" t="s">
+      <c r="A17" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="13" t="s">
+      <c r="B17" s="15">
+        <v>46189.0</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="F17" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="14">
+      <c r="G17" s="16">
         <v>50.0</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>21</v>
+        <v>29</v>
+      </c>
+      <c r="B18" s="12">
+        <v>46189.0</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D18" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="F18" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="12">
+      <c r="G18" s="13">
         <v>270.0</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="13" t="s">
+      <c r="A19" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="13" t="s">
+      <c r="B19" s="15">
+        <v>46189.0</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="F19" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F19" s="14">
+      <c r="G19" s="16">
         <v>30.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>21</v>
+        <v>32</v>
+      </c>
+      <c r="B20" s="12">
+        <v>46189.0</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D20" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="F20" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="12">
+      <c r="G20" s="13">
         <v>150.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" s="13" t="s">
+      <c r="A21" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" s="13" t="s">
+      <c r="B21" s="15">
+        <v>46190.0</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="F21" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="14">
+      <c r="G21" s="16">
         <v>150.0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="11" t="s">
         <v>34</v>
       </c>
+      <c r="B22" s="12">
+        <v>46190.0</v>
+      </c>
       <c r="C22" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="13">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="12">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" s="13" t="s">
+      <c r="B23" s="15">
+        <v>46190.0</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="F23" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="14">
+      <c r="G23" s="16">
         <v>200.0</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="12">
+        <v>46190.0</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="11" t="s">
+      <c r="E24" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F24" s="12">
+      <c r="F24" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G24" s="13">
         <v>100.0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="13" t="s">
+      <c r="A25" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" s="13" t="s">
+      <c r="B25" s="15">
+        <v>46190.0</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="F25" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F25" s="14">
+      <c r="G25" s="16">
         <v>100.0</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="12">
+        <v>46190.0</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="11" t="s">
+      <c r="E26" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E26" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F26" s="12">
+      <c r="F26" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G26" s="13">
         <v>100.0</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="13" t="s">
+      <c r="A27" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" s="13" t="s">
+      <c r="B27" s="15">
+        <v>46191.0</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="F27" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="14">
+      <c r="G27" s="16">
         <v>55.0</v>
       </c>
-      <c r="G27" s="15" t="s">
-        <v>41</v>
+      <c r="H27" s="17" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="11" t="s">
         <v>43</v>
       </c>
+      <c r="B28" s="12">
+        <v>46191.0</v>
+      </c>
       <c r="C28" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D28" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="F28" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="12">
+      <c r="G28" s="13">
         <v>75.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C29" s="13" t="s">
+      <c r="A29" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="B29" s="15">
+        <v>46191.0</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="13" t="s">
+      <c r="F29" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F29" s="14">
+      <c r="G29" s="16">
         <v>20.0</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>21</v>
+        <v>46</v>
+      </c>
+      <c r="B30" s="12">
+        <v>46191.0</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="D30" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E30" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F30" s="12">
+      <c r="F30" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G30" s="13">
         <v>150.0</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="F31" s="14">
-        <v>200.0</v>
+      <c r="A31" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="15">
+        <v>46191.0</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31" s="16">
+        <v>100.0</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>21</v>
+        <v>48</v>
+      </c>
+      <c r="B32" s="12">
+        <v>46192.0</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="D32" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F32" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="12">
+      <c r="G32" s="13">
+        <v>70.0</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="15">
+        <v>46192.0</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G33" s="16">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" s="12">
+        <v>46192.0</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="G34" s="13">
         <v>100.0</v>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="13"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="14"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" s="15">
+        <v>46192.0</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G35" s="16">
+        <v>50.0</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="12">
+        <v>46192.0</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" s="13">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B37" s="15">
+        <v>46192.0</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" s="16">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="12">
+        <v>46192.0</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" s="13">
+        <v>100.0</v>
+      </c>
+    </row>
     <row r="39" ht="15.75" customHeight="1"/>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -2107,12 +2311,39 @@
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$A$13:$F$33"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="31">
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -9,16 +9,16 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="9/jUrh7nvB2edeN/pbrzDAS+gzkAXuqdV/eXyrMK0nY="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="OoFnF6o6IWdJXiwt5nHJInhqTvUYza4kEQojeiGs8KU="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="57">
-  <si>
-    <t>Updated as on June 20, 2026</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="68">
+  <si>
+    <t>Updated as on June 22, 2026</t>
   </si>
   <si>
     <t>Player</t>
@@ -48,145 +48,178 @@
     <t>Laakha</t>
   </si>
   <si>
+    <t>Laltu</t>
+  </si>
+  <si>
     <t>Mantekwal</t>
   </si>
   <si>
+    <t>Peterza</t>
+  </si>
+  <si>
+    <t>TenWall</t>
+  </si>
+  <si>
+    <t>Yogi</t>
+  </si>
+  <si>
+    <t>Total Bets</t>
+  </si>
+  <si>
+    <t>Match</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Prediction</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Winner</t>
+  </si>
+  <si>
+    <t>Loser</t>
+  </si>
+  <si>
+    <t>Points</t>
+  </si>
+  <si>
+    <t>Uruguay vs Cabo Verde</t>
+  </si>
+  <si>
+    <t>Uruguay</t>
+  </si>
+  <si>
+    <t>Draw</t>
+  </si>
+  <si>
+    <t>Spain vs Saudi Arabia</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Germany vs Côte d'Ivoire</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Netherlands vs Sweden</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>USA vs Australia</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>Türkiye vs Paraguay</t>
+  </si>
+  <si>
+    <t>Türkiye</t>
+  </si>
+  <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
+    <t>Brazil vs Haiti</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Scotland vs Morocco</t>
+  </si>
+  <si>
+    <t>Morocco</t>
+  </si>
+  <si>
+    <t>Canada vs Qatar</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Switzerland vs Bosnia &amp; Herz.</t>
+  </si>
+  <si>
+    <t>Switzerland</t>
+  </si>
+  <si>
+    <t>Qatar</t>
+  </si>
+  <si>
+    <t>Mexico vs Korea Republic</t>
+  </si>
+  <si>
+    <t>Mexico</t>
+  </si>
+  <si>
+    <t>Tenwall</t>
+  </si>
+  <si>
     <t>Peteza</t>
   </si>
   <si>
-    <t>TenWall</t>
-  </si>
-  <si>
-    <t>Total Bets</t>
-  </si>
-  <si>
-    <t>Match</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Prediction</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Winner</t>
-  </si>
-  <si>
-    <t>Loser</t>
-  </si>
-  <si>
-    <t>Points</t>
+    <t>England vs Croatia</t>
+  </si>
+  <si>
+    <t>England</t>
+  </si>
+  <si>
+    <t>Croatia</t>
+  </si>
+  <si>
+    <t>Portugal vs Congo DR</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
+    <t>IR Iran vs New Zealand</t>
+  </si>
+  <si>
+    <t>IR Iran</t>
+  </si>
+  <si>
+    <t>Belgium vs Egypt</t>
+  </si>
+  <si>
+    <t>Argentina vs Algeria</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>France vs Senegal</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Germany vs CuraÃ§ao</t>
+  </si>
+  <si>
+    <t>Not Draw</t>
   </si>
   <si>
     <t>Canada vs Bosnia &amp; Herz.</t>
   </si>
   <si>
-    <t>Draw</t>
-  </si>
-  <si>
     <t>USA vs Paraguay</t>
-  </si>
-  <si>
-    <t>USA</t>
-  </si>
-  <si>
-    <t>Germany vs CuraÃ§ao</t>
-  </si>
-  <si>
-    <t>Not Draw</t>
-  </si>
-  <si>
-    <t>IR Iran vs New Zealand</t>
-  </si>
-  <si>
-    <t>IR Iran</t>
-  </si>
-  <si>
-    <t>Belgium vs Egypt</t>
-  </si>
-  <si>
-    <t>Argentina vs Algeria</t>
-  </si>
-  <si>
-    <t>Argentina</t>
-  </si>
-  <si>
-    <t>France vs Senegal</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t>England vs Croatia</t>
-  </si>
-  <si>
-    <t>England</t>
-  </si>
-  <si>
-    <t>Croatia</t>
-  </si>
-  <si>
-    <t>Tenwall</t>
-  </si>
-  <si>
-    <t>Portugal vs Congo DR</t>
-  </si>
-  <si>
-    <t>Portugal</t>
-  </si>
-  <si>
-    <t>Canada vs Qatar</t>
-  </si>
-  <si>
-    <t>Canada</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>Switzerland vs Bosnia &amp; Herz.</t>
-  </si>
-  <si>
-    <t>Switzerland</t>
-  </si>
-  <si>
-    <t>Qatar</t>
-  </si>
-  <si>
-    <t>Mexico vs Korea Republic</t>
-  </si>
-  <si>
-    <t>Mexico</t>
-  </si>
-  <si>
-    <t>USA vs Australia</t>
-  </si>
-  <si>
-    <t>Türkiye vs Paraguay</t>
-  </si>
-  <si>
-    <t>Türkiye</t>
-  </si>
-  <si>
-    <t>Paraguay</t>
-  </si>
-  <si>
-    <t>Brazil vs Haiti</t>
-  </si>
-  <si>
-    <t>Brazil</t>
-  </si>
-  <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>Scotland vs Morocco</t>
-  </si>
-  <si>
-    <t>Morocco</t>
   </si>
 </sst>
 </file>
@@ -205,13 +238,16 @@
     </font>
     <font>
       <b/>
+      <sz val="8.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font/>
     <font>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <sz val="8.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="8.0"/>
@@ -250,7 +286,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border/>
     <border>
       <left style="thin">
@@ -264,17 +300,6 @@
       </bottom>
     </border>
     <border>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -300,7 +325,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -308,48 +333,51 @@
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="4" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -572,792 +600,981 @@
     <col customWidth="1" min="7" max="7" width="4.63"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
       <c r="G1" s="3"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="D2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3"/>
       <c r="F2" s="3"/>
-      <c r="G2" s="5" t="s">
-        <v>4</v>
-      </c>
+      <c r="G2" s="3"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="7">
-        <v>130.0</v>
-      </c>
-      <c r="E3" s="7">
+      <c r="B3" s="8">
+        <v>230.0</v>
+      </c>
+      <c r="C3" s="8">
         <v>0.0</v>
       </c>
-      <c r="G3" s="7">
-        <f t="shared" ref="G3:G10" si="1">C3-E3</f>
-        <v>130</v>
-      </c>
+      <c r="D3" s="8">
+        <f t="shared" ref="D3:D11" si="1">B3-C3</f>
+        <v>230</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="9">
+      <c r="B4" s="10">
         <v>380.0</v>
       </c>
-      <c r="E4" s="9">
+      <c r="C4" s="10">
         <v>220.0</v>
       </c>
-      <c r="G4" s="9">
+      <c r="D4" s="10">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="7">
+      <c r="B5" s="8">
+        <v>500.0</v>
+      </c>
+      <c r="C5" s="8">
+        <v>70.0</v>
+      </c>
+      <c r="D5" s="8">
+        <f t="shared" si="1"/>
+        <v>430</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="10">
+        <v>500.0</v>
+      </c>
+      <c r="C6" s="10">
+        <v>1050.0</v>
+      </c>
+      <c r="D6" s="10">
+        <f t="shared" si="1"/>
+        <v>-550</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="8">
         <v>400.0</v>
       </c>
-      <c r="E5" s="7">
-        <v>70.0</v>
-      </c>
-      <c r="G5" s="7">
-        <f t="shared" si="1"/>
-        <v>330</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="9">
-        <v>500.0</v>
-      </c>
-      <c r="E6" s="9">
-        <v>890.0</v>
-      </c>
-      <c r="G6" s="9">
-        <f t="shared" si="1"/>
-        <v>-390</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="7">
-        <v>400.0</v>
-      </c>
-      <c r="E7" s="7">
+      <c r="C7" s="8">
         <v>30.0</v>
       </c>
-      <c r="G7" s="7">
+      <c r="D7" s="8">
         <f t="shared" si="1"/>
         <v>370</v>
       </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="9">
+      <c r="B8" s="10">
+        <v>60.0</v>
+      </c>
+      <c r="C8" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="D8" s="10">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="8">
         <v>250.0</v>
       </c>
-      <c r="E8" s="9">
+      <c r="C9" s="8">
         <v>50.0</v>
       </c>
-      <c r="G8" s="9">
+      <c r="D9" s="8">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="6" t="s">
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="10">
+        <v>395.0</v>
+      </c>
+      <c r="C10" s="10">
+        <v>200.0</v>
+      </c>
+      <c r="D10" s="10">
+        <f t="shared" si="1"/>
+        <v>195</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="8">
+        <v>510.0</v>
+      </c>
+      <c r="C11" s="8">
+        <v>1805.0</v>
+      </c>
+      <c r="D11" s="8">
+        <f t="shared" si="1"/>
+        <v>-1295</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="10">
+        <v>200.0</v>
+      </c>
+      <c r="C12" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="D12" s="10">
+        <v>200.0</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="11">
+        <f>SUM(B3:B12)</f>
+        <v>3425</v>
+      </c>
+      <c r="C13" s="11">
+        <f>SUM(C3:C11)</f>
+        <v>3425</v>
+      </c>
+      <c r="D13" s="12">
+        <f>SUM(D3:D12)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="14">
+        <v>46194.0</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="10">
+        <v>200.0</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="16">
+        <v>46194.0</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="8">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="14">
+        <v>46193.0</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="10">
+        <v>65.0</v>
+      </c>
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="16">
+        <v>46193.0</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="8">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="14">
+        <v>46193.0</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="10">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="16">
+        <v>46193.0</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="8">
+        <v>160.0</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="14">
+        <v>46192.0</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G22" s="10">
+        <v>70.0</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="16">
+        <v>46192.0</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23" s="8">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="14">
+        <v>46192.0</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="10">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="16">
+        <v>46192.0</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="G25" s="8">
+        <v>50.0</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="14">
+        <v>46192.0</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="10">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="16">
+        <v>46192.0</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="8">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="14">
+        <v>46192.0</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="10">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="16">
+        <v>46191.0</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="8">
+        <v>55.0</v>
+      </c>
+      <c r="H29" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B30" s="14">
+        <v>46191.0</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G30" s="10">
+        <v>75.0</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="16">
+        <v>46191.0</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="G31" s="8">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="14">
+        <v>46191.0</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E32" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="7">
-        <v>330.0</v>
-      </c>
-      <c r="E9" s="7">
+      <c r="F32" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G32" s="10">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="16">
+        <v>46191.0</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G33" s="8">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" s="14">
+        <v>46190.0</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G34" s="10">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" s="18">
+        <v>46190.0</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="8">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="14">
+        <v>46190.0</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="10">
         <v>200.0</v>
       </c>
-      <c r="G9" s="7">
-        <f t="shared" si="1"/>
-        <v>130</v>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="9">
-        <v>350.0</v>
-      </c>
-      <c r="E10" s="9">
-        <v>1280.0</v>
-      </c>
-      <c r="G10" s="9">
-        <f t="shared" si="1"/>
-        <v>-930</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="4" t="s">
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" s="18">
+        <v>46190.0</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G37" s="8">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="14">
+        <v>46190.0</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G38" s="10">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" s="18">
+        <v>46190.0</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G39" s="8">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40" s="14">
+        <v>46189.0</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G40" s="10">
+        <v>50.0</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41" s="18">
+        <v>46189.0</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" s="8">
+        <v>270.0</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B42" s="14">
+        <v>46189.0</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G42" s="10">
+        <v>30.0</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B43" s="18">
+        <v>46189.0</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F43" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4">
-        <f>SUM(C3:C10)</f>
-        <v>2740</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="4">
-        <f>SUM(E3:F10)</f>
-        <v>2740</v>
-      </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="5">
-        <f>SUM(G3:G10)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="12">
+      <c r="G43" s="8">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B44" s="14">
+        <v>46187.0</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="10">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B45" s="18">
         <v>46186.0</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="11" t="s">
+      <c r="C45" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E45" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="13">
+      <c r="F45" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="8">
         <v>230.0</v>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="15">
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B46" s="14">
         <v>46186.0</v>
       </c>
-      <c r="C15" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="14" t="s">
+      <c r="C46" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E46" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F46" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G46" s="10">
         <v>80.0</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="12">
-        <v>46187.0</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="G16" s="13">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="15">
-        <v>46189.0</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="16">
-        <v>50.0</v>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="12">
-        <v>46189.0</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" s="13">
-        <v>270.0</v>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="15">
-        <v>46189.0</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19" s="16">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="12">
-        <v>46189.0</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="13">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" s="15">
-        <v>46190.0</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="G21" s="16">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="12">
-        <v>46190.0</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="13">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="15">
-        <v>46190.0</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23" s="16">
-        <v>200.0</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="12">
-        <v>46190.0</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="G24" s="13">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="15">
-        <v>46190.0</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="G25" s="16">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="12">
-        <v>46190.0</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="G26" s="13">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="15">
-        <v>46191.0</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="G27" s="16">
-        <v>55.0</v>
-      </c>
-      <c r="H27" s="17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="12">
-        <v>46191.0</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="G28" s="13">
-        <v>75.0</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="15">
-        <v>46191.0</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G29" s="16">
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30" s="12">
-        <v>46191.0</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="G30" s="13">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="15">
-        <v>46191.0</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="G31" s="16">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32" s="12">
-        <v>46192.0</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G32" s="13">
-        <v>70.0</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B33" s="15">
-        <v>46192.0</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E33" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G33" s="16">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B34" s="12">
-        <v>46192.0</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="G34" s="13">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B35" s="15">
-        <v>46192.0</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G35" s="16">
-        <v>50.0</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" s="12">
-        <v>46192.0</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G36" s="13">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B37" s="15">
-        <v>46192.0</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G37" s="16">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B38" s="12">
-        <v>46192.0</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G38" s="13">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
     <row r="47" ht="15.75" customHeight="1"/>
     <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
@@ -2311,39 +2528,11 @@
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -16,9 +16,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="68">
-  <si>
-    <t>Updated as on June 22, 2026</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="83">
+  <si>
+    <t>Updated as on June 23, 2026</t>
   </si>
   <si>
     <t>Player</t>
@@ -87,15 +87,45 @@
     <t>Points</t>
   </si>
   <si>
+    <t>Argentina vs Austria</t>
+  </si>
+  <si>
+    <t>22-06-26</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>France vs Iraq</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Norway vs Senegal</t>
+  </si>
+  <si>
+    <t>Draw</t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
+    <t>Jordan vs Algeria</t>
+  </si>
+  <si>
+    <t>Algeria</t>
+  </si>
+  <si>
     <t>Uruguay vs Cabo Verde</t>
   </si>
   <si>
+    <t>21-06-26</t>
+  </si>
+  <si>
     <t>Uruguay</t>
   </si>
   <si>
-    <t>Draw</t>
-  </si>
-  <si>
     <t>Spain vs Saudi Arabia</t>
   </si>
   <si>
@@ -105,6 +135,9 @@
     <t>Germany vs Côte d'Ivoire</t>
   </si>
   <si>
+    <t>20-06-26</t>
+  </si>
+  <si>
     <t>Germany</t>
   </si>
   <si>
@@ -114,9 +147,15 @@
     <t>Netherlands</t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t>USA vs Australia</t>
   </si>
   <si>
+    <t>19-06-26</t>
+  </si>
+  <si>
     <t>USA</t>
   </si>
   <si>
@@ -147,12 +186,12 @@
     <t>Canada vs Qatar</t>
   </si>
   <si>
+    <t>18-06-26</t>
+  </si>
+  <si>
     <t>Canada</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>Switzerland vs Bosnia &amp; Herz.</t>
   </si>
   <si>
@@ -177,6 +216,9 @@
     <t>England vs Croatia</t>
   </si>
   <si>
+    <t>17-06-26</t>
+  </si>
+  <si>
     <t>England</t>
   </si>
   <si>
@@ -192,6 +234,9 @@
     <t>IR Iran vs New Zealand</t>
   </si>
   <si>
+    <t>16-06-26</t>
+  </si>
+  <si>
     <t>IR Iran</t>
   </si>
   <si>
@@ -201,16 +246,16 @@
     <t>Argentina vs Algeria</t>
   </si>
   <si>
-    <t>Argentina</t>
+    <t>15-06-26</t>
   </si>
   <si>
     <t>France vs Senegal</t>
   </si>
   <si>
-    <t>France</t>
-  </si>
-  <si>
     <t>Germany vs CuraÃ§ao</t>
+  </si>
+  <si>
+    <t>14-06-26</t>
   </si>
   <si>
     <t>Not Draw</t>
@@ -227,7 +272,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="d mmmm"/>
+    <numFmt numFmtId="164" formatCode="mm-dd-yy"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -260,7 +305,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -285,8 +330,20 @@
         <bgColor rgb="FF9BC2E6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8CB5F9"/>
+        <bgColor rgb="FF8CB5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E7FD"/>
+        <bgColor rgb="FFD9E7FD"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border/>
     <border>
       <left style="thin">
@@ -311,6 +368,14 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -325,7 +390,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -334,13 +399,13 @@
     </xf>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -358,26 +423,35 @@
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="6" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -595,8 +669,8 @@
     <col customWidth="1" min="1" max="1" width="14.75"/>
     <col customWidth="1" min="2" max="3" width="5.38"/>
     <col customWidth="1" min="4" max="4" width="6.5"/>
-    <col customWidth="1" min="5" max="5" width="6.38"/>
-    <col customWidth="1" min="6" max="6" width="6.5"/>
+    <col customWidth="1" min="5" max="5" width="5.63"/>
+    <col customWidth="1" min="6" max="6" width="5.25"/>
     <col customWidth="1" min="7" max="7" width="4.63"/>
   </cols>
   <sheetData>
@@ -633,14 +707,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="8">
-        <v>230.0</v>
+        <v>330.0</v>
       </c>
       <c r="C3" s="8">
         <v>0.0</v>
       </c>
       <c r="D3" s="8">
-        <f t="shared" ref="D3:D11" si="1">B3-C3</f>
-        <v>230</v>
+        <v>330.0</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -651,14 +724,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="10">
-        <v>380.0</v>
+        <v>420.0</v>
       </c>
       <c r="C4" s="10">
-        <v>220.0</v>
+        <v>235.0</v>
       </c>
       <c r="D4" s="10">
-        <f t="shared" si="1"/>
-        <v>160</v>
+        <v>185.0</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -672,11 +744,10 @@
         <v>500.0</v>
       </c>
       <c r="C5" s="8">
-        <v>70.0</v>
+        <v>310.0</v>
       </c>
       <c r="D5" s="8">
-        <f t="shared" si="1"/>
-        <v>430</v>
+        <v>190.0</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -693,8 +764,7 @@
         <v>1050.0</v>
       </c>
       <c r="D6" s="10">
-        <f t="shared" si="1"/>
-        <v>-550</v>
+        <v>-550.0</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -711,8 +781,7 @@
         <v>30.0</v>
       </c>
       <c r="D7" s="8">
-        <f t="shared" si="1"/>
-        <v>370</v>
+        <v>370.0</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -723,14 +792,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="10">
-        <v>60.0</v>
+        <v>100.0</v>
       </c>
       <c r="C8" s="10">
+        <v>100.0</v>
+      </c>
+      <c r="D8" s="10">
         <v>0.0</v>
-      </c>
-      <c r="D8" s="10">
-        <f t="shared" si="1"/>
-        <v>60</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -740,14 +808,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="8">
-        <v>250.0</v>
+        <v>350.0</v>
       </c>
       <c r="C9" s="8">
-        <v>50.0</v>
+        <v>130.0</v>
       </c>
       <c r="D9" s="8">
-        <f t="shared" si="1"/>
-        <v>200</v>
+        <v>220.0</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -758,14 +825,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="10">
-        <v>395.0</v>
+        <v>450.0</v>
       </c>
       <c r="C10" s="10">
         <v>200.0</v>
       </c>
       <c r="D10" s="10">
-        <f t="shared" si="1"/>
-        <v>195</v>
+        <v>250.0</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -776,14 +842,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="8">
-        <v>510.0</v>
+        <v>710.0</v>
       </c>
       <c r="C11" s="8">
-        <v>1805.0</v>
+        <v>1905.0</v>
       </c>
       <c r="D11" s="8">
-        <f t="shared" si="1"/>
-        <v>-1295</v>
+        <v>-1195.0</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -810,17 +875,14 @@
       <c r="A13" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="11">
-        <f>SUM(B3:B12)</f>
-        <v>3425</v>
-      </c>
-      <c r="C13" s="11">
-        <f>SUM(C3:C11)</f>
-        <v>3425</v>
-      </c>
-      <c r="D13" s="12">
-        <f>SUM(D3:D12)</f>
-        <v>0</v>
+      <c r="B13" s="12">
+        <v>3960.0</v>
+      </c>
+      <c r="C13" s="12">
+        <v>3960.0</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0.0</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -836,115 +898,115 @@
       <c r="G14" s="13"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="G15" s="14" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="14">
-        <v>46194.0</v>
-      </c>
-      <c r="C16" s="9" t="s">
+      <c r="B16" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="C16" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="9" t="s">
+      <c r="D16" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="16">
+        <v>40.0</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G17" s="8">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="G16" s="10">
-        <v>200.0</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="16">
-        <v>46194.0</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="15" t="s">
+      <c r="F18" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="8">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="14">
-        <v>46193.0</v>
-      </c>
-      <c r="C18" s="9" t="s">
+      <c r="G18" s="16">
+        <v>100.0</v>
+      </c>
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="10">
-        <v>65.0</v>
-      </c>
-      <c r="J18" s="3"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="16">
-        <v>46193.0</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" s="15" t="s">
+      <c r="D19" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="17" t="s">
         <v>13</v>
       </c>
       <c r="G19" s="8">
@@ -952,637 +1014,813 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="14">
-        <v>46193.0</v>
-      </c>
-      <c r="C20" s="9" t="s">
+      <c r="D20" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="16">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="9" t="s">
+      <c r="E21" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="G21" s="8">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="16">
+        <v>40.0</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="8">
+        <v>40.0</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G24" s="16">
+        <v>200.0</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="8">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="16">
+        <v>65.0</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="8">
         <v>100.0</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="16">
-        <v>46193.0</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="15" t="s">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="F21" s="15" t="s">
+      <c r="G28" s="16">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G29" s="8">
         <v>160.0</v>
       </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="14">
-        <v>46192.0</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="9" t="s">
+      <c r="H29" s="19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F30" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G30" s="16">
         <v>70.0</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="16">
-        <v>46192.0</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="15" t="s">
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E31" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="F31" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G31" s="8">
         <v>150.0</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="14">
-        <v>46192.0</v>
-      </c>
-      <c r="C24" s="9" t="s">
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="16">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G33" s="8">
+        <v>50.0</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="16">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="8">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="16">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G37" s="8">
+        <v>55.0</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G38" s="16">
+        <v>75.0</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G39" s="8">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="G40" s="16">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="G41" s="8">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G42" s="16">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="8">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" s="16">
+        <v>200.0</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="G45" s="8">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E46" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="G46" s="16">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D47" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="G47" s="8">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E48" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G48" s="16">
+        <v>50.0</v>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="B49" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D49" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="F49" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49" s="8">
+        <v>270.0</v>
+      </c>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C50" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="9" t="s">
+      <c r="D50" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F50" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G50" s="16">
+        <v>30.0</v>
+      </c>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B51" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C51" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D51" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F51" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="G51" s="8">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E52" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F52" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G52" s="16">
         <v>100.0</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="16">
-        <v>46192.0</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" s="15" t="s">
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B53" s="20">
+        <v>46362.0</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D53" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="8">
+        <v>230.0</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B54" s="21">
+        <v>46362.0</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E54" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="G25" s="8">
-        <v>50.0</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="14">
-        <v>46192.0</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" s="10">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="16">
-        <v>46192.0</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="8">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="14">
-        <v>46192.0</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E28" s="9" t="s">
+      <c r="F54" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="10">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="16">
-        <v>46191.0</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="8">
-        <v>55.0</v>
-      </c>
-      <c r="H29" s="17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" s="14">
-        <v>46191.0</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="G30" s="10">
-        <v>75.0</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="16">
-        <v>46191.0</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G31" s="8">
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32" s="14">
-        <v>46191.0</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G32" s="10">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="16">
-        <v>46191.0</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="E33" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="G33" s="8">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B34" s="14">
-        <v>46190.0</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="G34" s="10">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B35" s="18">
-        <v>46190.0</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="E35" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="F35" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G35" s="8">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B36" s="14">
-        <v>46190.0</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="10">
-        <v>200.0</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B37" s="18">
-        <v>46190.0</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="E37" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="G37" s="8">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B38" s="14">
-        <v>46190.0</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G38" s="10">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B39" s="18">
-        <v>46190.0</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="E39" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F39" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="G39" s="8">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B40" s="14">
-        <v>46189.0</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G40" s="10">
-        <v>50.0</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B41" s="18">
-        <v>46189.0</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E41" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="F41" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G41" s="8">
-        <v>270.0</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B42" s="14">
-        <v>46189.0</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G42" s="10">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="B43" s="18">
-        <v>46189.0</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E43" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G43" s="8">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B44" s="14">
-        <v>46187.0</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="G44" s="10">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="B45" s="18">
-        <v>46186.0</v>
-      </c>
-      <c r="C45" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D45" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E45" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G45" s="8">
-        <v>230.0</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="B46" s="14">
-        <v>46186.0</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="G46" s="10">
+      <c r="G54" s="16">
         <v>80.0</v>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
     <row r="55" ht="15.75" customHeight="1"/>
     <row r="56" ht="15.75" customHeight="1"/>
     <row r="57" ht="15.75" customHeight="1"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -9,16 +9,16 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="OoFnF6o6IWdJXiwt5nHJInhqTvUYza4kEQojeiGs8KU="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="wM08Me0VgXeAXrxvisDvg/6NmRORXupD0Hmt14831fs="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="83">
-  <si>
-    <t>Updated as on June 23, 2026</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="86">
+  <si>
+    <t>Updated as on June 24, 2026</t>
   </si>
   <si>
     <t>Player</t>
@@ -87,30 +87,45 @@
     <t>Points</t>
   </si>
   <si>
+    <t>Colombia vs Congo DR</t>
+  </si>
+  <si>
+    <t>23-06-26</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>Panama vs Croatia</t>
+  </si>
+  <si>
+    <t>Croatia</t>
+  </si>
+  <si>
+    <t>France vs Iraq</t>
+  </si>
+  <si>
+    <t>22-06-26</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Norway vs Senegal</t>
+  </si>
+  <si>
+    <t>Draw</t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
     <t>Argentina vs Austria</t>
   </si>
   <si>
-    <t>22-06-26</t>
-  </si>
-  <si>
     <t>Argentina</t>
   </si>
   <si>
-    <t>France vs Iraq</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t>Norway vs Senegal</t>
-  </si>
-  <si>
-    <t>Draw</t>
-  </si>
-  <si>
-    <t>Norway</t>
-  </si>
-  <si>
     <t>Jordan vs Algeria</t>
   </si>
   <si>
@@ -147,9 +162,6 @@
     <t>Netherlands</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>USA vs Australia</t>
   </si>
   <si>
@@ -220,9 +232,6 @@
   </si>
   <si>
     <t>England</t>
-  </si>
-  <si>
-    <t>Croatia</t>
   </si>
   <si>
     <t>Portugal vs Congo DR</t>
@@ -274,7 +283,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm-dd-yy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -298,11 +307,6 @@
       <sz val="8.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -332,18 +336,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD9E7FD"/>
+        <bgColor rgb="FFD9E7FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF8CB5F9"/>
         <bgColor rgb="FF8CB5F9"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E7FD"/>
-        <bgColor rgb="FFD9E7FD"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="9">
     <border/>
     <border>
       <left style="thin">
@@ -386,11 +390,34 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -408,23 +435,32 @@
     <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="5" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="6" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="6" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="8" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -432,25 +468,22 @@
     <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="0" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="6" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -712,7 +745,7 @@
       <c r="C3" s="8">
         <v>0.0</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="9">
         <v>330.0</v>
       </c>
       <c r="E3" s="3"/>
@@ -720,17 +753,17 @@
       <c r="G3" s="3"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="10">
-        <v>420.0</v>
-      </c>
-      <c r="C4" s="10">
+      <c r="B4" s="11">
+        <v>490.0</v>
+      </c>
+      <c r="C4" s="11">
         <v>235.0</v>
       </c>
-      <c r="D4" s="10">
-        <v>185.0</v>
+      <c r="D4" s="12">
+        <v>255.0</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -744,27 +777,27 @@
         <v>500.0</v>
       </c>
       <c r="C5" s="8">
-        <v>310.0</v>
-      </c>
-      <c r="D5" s="8">
-        <v>190.0</v>
+        <v>450.0</v>
+      </c>
+      <c r="D5" s="9">
+        <v>50.0</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="11">
         <v>500.0</v>
       </c>
-      <c r="C6" s="10">
-        <v>1050.0</v>
-      </c>
-      <c r="D6" s="10">
-        <v>-550.0</v>
+      <c r="C6" s="11">
+        <v>1130.0</v>
+      </c>
+      <c r="D6" s="12">
+        <v>-630.0</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -780,7 +813,7 @@
       <c r="C7" s="8">
         <v>30.0</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="9">
         <v>370.0</v>
       </c>
       <c r="E7" s="3"/>
@@ -788,16 +821,16 @@
       <c r="G7" s="3"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="11">
         <v>100.0</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="11">
         <v>100.0</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="12">
         <v>0.0</v>
       </c>
       <c r="E8" s="3"/>
@@ -813,7 +846,7 @@
       <c r="C9" s="8">
         <v>130.0</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="9">
         <v>220.0</v>
       </c>
       <c r="E9" s="3"/>
@@ -821,16 +854,16 @@
       <c r="G9" s="3"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="11">
         <v>450.0</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="11">
         <v>200.0</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="12">
         <v>250.0</v>
       </c>
       <c r="E10" s="3"/>
@@ -842,29 +875,29 @@
         <v>13</v>
       </c>
       <c r="B11" s="8">
-        <v>710.0</v>
+        <v>860.0</v>
       </c>
       <c r="C11" s="8">
         <v>1905.0</v>
       </c>
-      <c r="D11" s="8">
-        <v>-1195.0</v>
+      <c r="D11" s="9">
+        <v>-1045.0</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="11">
         <v>200.0</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="11">
         <v>0.0</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="12">
         <v>200.0</v>
       </c>
       <c r="E12" s="3"/>
@@ -872,16 +905,16 @@
       <c r="G12" s="3"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="12">
-        <v>3960.0</v>
-      </c>
-      <c r="C13" s="12">
-        <v>3960.0</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="B13" s="14">
+        <v>4180.0</v>
+      </c>
+      <c r="C13" s="14">
+        <v>4180.0</v>
+      </c>
+      <c r="D13" s="15">
         <v>0.0</v>
       </c>
       <c r="E13" s="3"/>
@@ -889,941 +922,1003 @@
       <c r="G13" s="3"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="8">
+        <v>70.0</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="21">
+        <v>70.0</v>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="8">
+        <v>80.0</v>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F19" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="21">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="8">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G21" s="21">
         <v>40.0</v>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="17" t="s">
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="8">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" s="21">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" s="8">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" s="21">
+        <v>40.0</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="8">
+        <v>40.0</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="21">
+        <v>200.0</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="8">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" s="21">
+        <v>65.0</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="8">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="21">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="8">
+        <v>160.0</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G33" s="21">
+        <v>70.0</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="G34" s="8">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="21">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="G36" s="8">
+        <v>50.0</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="21">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="8">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="21">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D40" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F40" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G40" s="8">
+        <v>55.0</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F41" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" s="21">
+        <v>75.0</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D42" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E42" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="G42" s="8">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D43" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G43" s="21">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="E44" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G44" s="8">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D45" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="21">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D46" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E46" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="F46" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G46" s="8">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="21">
+        <v>200.0</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C48" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D48" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E48" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="G48" s="8">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B49" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="G49" s="21">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="17" t="s">
+      <c r="D50" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E50" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="G17" s="8">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="15" t="s">
+      <c r="F50" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="G50" s="8">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C51" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D51" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G51" s="21">
+        <v>50.0</v>
+      </c>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C52" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E52" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="F52" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="8">
+        <v>270.0</v>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C53" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D53" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E53" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F53" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="G53" s="21">
+        <v>30.0</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D54" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E54" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F54" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="16">
+      <c r="G54" s="8">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B55" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C55" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D55" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E55" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="G55" s="21">
         <v>100.0</v>
       </c>
-      <c r="J18" s="3"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="17" t="s">
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B56" s="22">
+        <v>46362.0</v>
+      </c>
+      <c r="C56" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="17" t="s">
+      <c r="D56" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E56" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="8">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="G20" s="16">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G21" s="8">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="15" t="s">
+      <c r="G56" s="8">
+        <v>230.0</v>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B57" s="23">
+        <v>46362.0</v>
+      </c>
+      <c r="C57" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D57" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="E57" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22" s="16">
-        <v>40.0</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23" s="8">
-        <v>40.0</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="16">
-        <v>200.0</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" s="8">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" s="16">
-        <v>65.0</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="8">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="16">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" s="17" t="s">
+      <c r="F57" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="G29" s="8">
-        <v>160.0</v>
-      </c>
-      <c r="H29" s="19" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="G30" s="16">
-        <v>70.0</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="B31" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="G31" s="8">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G32" s="16">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="G33" s="8">
-        <v>50.0</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="16">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="B35" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C35" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D35" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E35" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" s="8">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E36" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="16">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B37" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="C37" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="D37" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G37" s="8">
-        <v>55.0</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="B38" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E38" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G38" s="16">
-        <v>75.0</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B39" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="C39" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="D39" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="E39" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="G39" s="8">
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B40" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E40" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="G40" s="16">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B41" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="C41" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D41" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="E41" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="G41" s="8">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="B42" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="E42" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G42" s="16">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="B43" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C43" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="D43" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E43" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="F43" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G43" s="8">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="B44" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C44" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="E44" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44" s="16">
-        <v>200.0</v>
-      </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="B45" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C45" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="D45" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E45" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="G45" s="8">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B46" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C46" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D46" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E46" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="G46" s="16">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="B47" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C47" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="D47" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E47" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F47" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="G47" s="8">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="B48" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C48" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D48" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E48" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G48" s="16">
-        <v>50.0</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="B49" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="C49" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D49" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E49" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="F49" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G49" s="8">
-        <v>270.0</v>
-      </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B50" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C50" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E50" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F50" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="G50" s="16">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="B51" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C51" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D51" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E51" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G51" s="8">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="B52" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C52" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D52" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="E52" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F52" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G52" s="16">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="B53" s="20">
-        <v>46362.0</v>
-      </c>
-      <c r="C53" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D53" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E53" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G53" s="8">
-        <v>230.0</v>
-      </c>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="B54" s="21">
-        <v>46362.0</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D54" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="E54" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F54" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="G54" s="16">
+      <c r="G57" s="21">
         <v>80.0</v>
       </c>
     </row>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
     <row r="58" ht="15.75" customHeight="1"/>
     <row r="59" ht="15.75" customHeight="1"/>
     <row r="60" ht="15.75" customHeight="1"/>
@@ -2768,6 +2863,9 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -9,17 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="wM08Me0VgXeAXrxvisDvg/6NmRORXupD0Hmt14831fs="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="3o8XtCDJASIl1ghMNIigoucMzfPr61Tg3hBgBpsse+U="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="86">
-  <si>
-    <t>Updated as on June 24, 2026</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
   <si>
     <t>Player</t>
   </si>
@@ -63,7 +60,7 @@
     <t>Yogi</t>
   </si>
   <si>
-    <t>Total Bets</t>
+    <t>Total</t>
   </si>
   <si>
     <t>Match</t>
@@ -87,6 +84,39 @@
     <t>Points</t>
   </si>
   <si>
+    <t>South Africa vs Korea Republic</t>
+  </si>
+  <si>
+    <t>24-06-26</t>
+  </si>
+  <si>
+    <t>Draw</t>
+  </si>
+  <si>
+    <t>Bosnia &amp; Herz. vs Qatar</t>
+  </si>
+  <si>
+    <t>Bosnia &amp; Herz.</t>
+  </si>
+  <si>
+    <t>Scotland vs Brazil</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>Switzerland vs Canada</t>
+  </si>
+  <si>
+    <t>Switzerland</t>
+  </si>
+  <si>
+    <t>Morocco vs Haiti</t>
+  </si>
+  <si>
+    <t>Morocco</t>
+  </si>
+  <si>
     <t>Colombia vs Congo DR</t>
   </si>
   <si>
@@ -114,9 +144,6 @@
     <t>Norway vs Senegal</t>
   </si>
   <si>
-    <t>Draw</t>
-  </si>
-  <si>
     <t>Norway</t>
   </si>
   <si>
@@ -183,18 +210,12 @@
     <t>Brazil vs Haiti</t>
   </si>
   <si>
-    <t>Brazil</t>
-  </si>
-  <si>
     <t>Australia</t>
   </si>
   <si>
     <t>Scotland vs Morocco</t>
   </si>
   <si>
-    <t>Morocco</t>
-  </si>
-  <si>
     <t>Canada vs Qatar</t>
   </si>
   <si>
@@ -205,9 +226,6 @@
   </si>
   <si>
     <t>Switzerland vs Bosnia &amp; Herz.</t>
-  </si>
-  <si>
-    <t>Switzerland</t>
   </si>
   <si>
     <t>Qatar</t>
@@ -280,10 +298,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mm-dd-yy"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="mmmm d, yyyy"/>
+    <numFmt numFmtId="165" formatCode="mm-dd-yy"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -292,7 +311,7 @@
     </font>
     <font>
       <b/>
-      <sz val="8.0"/>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
@@ -304,12 +323,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="8.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="8.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -318,14 +343,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
-        <bgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor rgb="FF00B0F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
         <bgColor rgb="FF00B050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -347,7 +378,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border/>
     <border>
       <left style="thin">
@@ -361,6 +392,17 @@
       </bottom>
     </border>
     <border>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -417,73 +459,74 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="6" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="6" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="6" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="8" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="9" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="8" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="6" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="7" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -708,1223 +751,1355 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1">
+        <v>46198.0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="s">
+      <c r="B3" s="9">
+        <v>330.0</v>
+      </c>
+      <c r="C3" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="D3" s="10">
+        <v>330.0</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="8">
-        <v>330.0</v>
-      </c>
-      <c r="C3" s="8">
+      <c r="B4" s="12">
+        <v>580.0</v>
+      </c>
+      <c r="C4" s="12">
+        <v>235.0</v>
+      </c>
+      <c r="D4" s="13">
+        <v>345.0</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="9">
+        <v>600.0</v>
+      </c>
+      <c r="C5" s="9">
+        <v>670.0</v>
+      </c>
+      <c r="D5" s="10">
+        <v>-70.0</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="12">
+        <v>500.0</v>
+      </c>
+      <c r="C6" s="12">
+        <v>1230.0</v>
+      </c>
+      <c r="D6" s="13">
+        <v>-730.0</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="9">
+        <v>500.0</v>
+      </c>
+      <c r="C7" s="9">
+        <v>120.0</v>
+      </c>
+      <c r="D7" s="10">
+        <v>380.0</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="12">
+        <v>100.0</v>
+      </c>
+      <c r="C8" s="12">
+        <v>100.0</v>
+      </c>
+      <c r="D8" s="13">
         <v>0.0</v>
       </c>
-      <c r="D3" s="9">
-        <v>330.0</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="s">
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="9">
+        <v>350.0</v>
+      </c>
+      <c r="C9" s="9">
+        <v>130.0</v>
+      </c>
+      <c r="D9" s="10">
+        <v>220.0</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="12">
+        <v>505.0</v>
+      </c>
+      <c r="C10" s="12">
+        <v>200.0</v>
+      </c>
+      <c r="D10" s="13">
+        <v>305.0</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="9">
+        <v>1080.0</v>
+      </c>
+      <c r="C11" s="9">
+        <v>2060.0</v>
+      </c>
+      <c r="D11" s="10">
+        <v>-980.0</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="12">
+        <v>200.0</v>
+      </c>
+      <c r="C12" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="D12" s="13">
+        <v>200.0</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="15">
+        <v>4745.0</v>
+      </c>
+      <c r="C13" s="15">
+        <v>4745.0</v>
+      </c>
+      <c r="D13" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="22">
+        <v>90.0</v>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="9">
+        <v>55.0</v>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="11">
-        <v>490.0</v>
-      </c>
-      <c r="C4" s="11">
-        <v>235.0</v>
-      </c>
-      <c r="D4" s="12">
-        <v>255.0</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="G19" s="22">
+        <v>130.0</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="G21" s="22">
+        <v>90.0</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="9">
+        <v>70.0</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23" s="22">
+        <v>70.0</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="8">
-        <v>500.0</v>
-      </c>
-      <c r="C5" s="8">
-        <v>450.0</v>
-      </c>
-      <c r="D5" s="9">
+      <c r="G24" s="9">
+        <v>80.0</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="G25" s="22">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G26" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="G27" s="22">
+        <v>40.0</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="G29" s="22">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G30" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="F31" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="22">
+        <v>40.0</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="9">
+        <v>40.0</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="22">
+        <v>200.0</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" s="9">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" s="22">
+        <v>65.0</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" s="22">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G38" s="9">
+        <v>160.0</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D39" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="F39" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="G39" s="22">
+        <v>70.0</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G40" s="9">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B41" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E41" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G41" s="22">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D42" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G42" s="9">
         <v>50.0</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="s">
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B43" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E43" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" s="22">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D44" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="E44" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="11">
-        <v>500.0</v>
-      </c>
-      <c r="C6" s="11">
-        <v>1130.0</v>
-      </c>
-      <c r="D6" s="12">
-        <v>-630.0</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="8">
-        <v>400.0</v>
-      </c>
-      <c r="C7" s="8">
+      <c r="F44" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" s="9">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E45" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" s="22">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C46" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G46" s="9">
+        <v>55.0</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B47" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C47" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D47" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E47" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G47" s="22">
+        <v>75.0</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="D48" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G48" s="9">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B49" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C49" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="E49" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="G49" s="22">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D50" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F50" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="G50" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B51" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C51" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="E51" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G51" s="22">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B52" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C52" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D52" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="E52" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="F52" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G52" s="9">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B53" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C53" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D53" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="E53" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G53" s="22">
+        <v>200.0</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B54" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D54" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="G54" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B55" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C55" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="D55" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F55" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="G55" s="22">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B56" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C56" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D56" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="E56" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F56" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="G56" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B57" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C57" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="D57" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F57" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G57" s="22">
+        <v>50.0</v>
+      </c>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="B58" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="C58" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D58" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="F58" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G58" s="9">
+        <v>270.0</v>
+      </c>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B59" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C59" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D59" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E59" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="22">
         <v>30.0</v>
       </c>
-      <c r="D7" s="9">
-        <v>370.0</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="11">
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B60" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C60" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D60" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="E60" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F60" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G60" s="9">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B61" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C61" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D61" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E61" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F61" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G61" s="22">
         <v>100.0</v>
       </c>
-      <c r="C8" s="11">
-        <v>100.0</v>
-      </c>
-      <c r="D8" s="12">
-        <v>0.0</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="8">
-        <v>350.0</v>
-      </c>
-      <c r="C9" s="8">
-        <v>130.0</v>
-      </c>
-      <c r="D9" s="9">
-        <v>220.0</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="10" t="s">
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B62" s="23">
+        <v>46362.0</v>
+      </c>
+      <c r="C62" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D62" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F62" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="11">
-        <v>450.0</v>
-      </c>
-      <c r="C10" s="11">
-        <v>200.0</v>
-      </c>
-      <c r="D10" s="12">
-        <v>250.0</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="8">
-        <v>860.0</v>
-      </c>
-      <c r="C11" s="8">
-        <v>1905.0</v>
-      </c>
-      <c r="D11" s="9">
-        <v>-1045.0</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="11">
-        <v>200.0</v>
-      </c>
-      <c r="C12" s="11">
-        <v>0.0</v>
-      </c>
-      <c r="D12" s="12">
-        <v>200.0</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="14">
-        <v>4180.0</v>
-      </c>
-      <c r="C13" s="14">
-        <v>4180.0</v>
-      </c>
-      <c r="D13" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" s="18" t="s">
+      <c r="G62" s="9">
+        <v>230.0</v>
+      </c>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B63" s="24">
+        <v>46362.0</v>
+      </c>
+      <c r="C63" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="E63" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="F63" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G16" s="8">
-        <v>70.0</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="G17" s="21">
-        <v>70.0</v>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" s="8">
+      <c r="G63" s="22">
         <v>80.0</v>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="G19" s="21">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="8">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="G21" s="21">
-        <v>40.0</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="8">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="G23" s="21">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="G24" s="8">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G25" s="21">
-        <v>40.0</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26" s="8">
-        <v>40.0</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="F27" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="21">
-        <v>200.0</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="8">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="E29" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" s="21">
-        <v>65.0</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="8">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="B31" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D31" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="E31" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="21">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C32" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D32" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="E32" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="G32" s="8">
-        <v>160.0</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B33" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="D33" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="E33" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="G33" s="21">
-        <v>70.0</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="C34" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="D34" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="G34" s="8">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="E35" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="G35" s="21">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="C36" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D36" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="E36" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="G36" s="8">
-        <v>50.0</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="B37" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E37" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37" s="21">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="C38" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="8">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E39" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" s="21">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C40" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D40" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="G40" s="8">
-        <v>55.0</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="B41" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="D41" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="E41" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F41" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="G41" s="21">
-        <v>75.0</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B42" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="D42" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="E42" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="G42" s="8">
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B43" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C43" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D43" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="E43" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="G43" s="21">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="B44" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C44" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D44" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="E44" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="G44" s="8">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="B45" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E45" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F45" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="G45" s="21">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="B46" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C46" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="D46" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="E46" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="F46" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="G46" s="8">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="B47" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C47" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D47" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E47" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G47" s="21">
-        <v>200.0</v>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="B48" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C48" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D48" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="E48" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="G48" s="8">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="B49" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C49" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="D49" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E49" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="G49" s="21">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="B50" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C50" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D50" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="E50" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F50" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="G50" s="8">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="B51" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C51" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="D51" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E51" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F51" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G51" s="21">
-        <v>50.0</v>
-      </c>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="B52" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C52" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D52" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E52" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="F52" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="G52" s="8">
-        <v>270.0</v>
-      </c>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="B53" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C53" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="D53" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="E53" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F53" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="G53" s="21">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="B54" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C54" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D54" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="E54" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54" s="8">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="B55" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C55" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D55" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="E55" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F55" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="G55" s="21">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="B56" s="22">
-        <v>46362.0</v>
-      </c>
-      <c r="C56" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D56" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E56" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" s="8">
-        <v>230.0</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="B57" s="23">
-        <v>46362.0</v>
-      </c>
-      <c r="C57" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="D57" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="E57" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F57" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="G57" s="21">
-        <v>80.0</v>
-      </c>
-    </row>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
     <row r="64" ht="15.75" customHeight="1"/>
     <row r="65" ht="15.75" customHeight="1"/>
     <row r="66" ht="15.75" customHeight="1"/>
@@ -2866,6 +3041,12 @@
     <row r="1002" ht="15.75" customHeight="1"/>
     <row r="1003" ht="15.75" customHeight="1"/>
     <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
+    <row r="1006" ht="15.75" customHeight="1"/>
+    <row r="1007" ht="15.75" customHeight="1"/>
+    <row r="1008" ht="15.75" customHeight="1"/>
+    <row r="1009" ht="15.75" customHeight="1"/>
+    <row r="1010" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="3o8XtCDJASIl1ghMNIigoucMzfPr61Tg3hBgBpsse+U="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="jS4b/Dq0CM/WvEdkf4U3k4wnEnJMQgs1O3DWezus6hk="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="125">
   <si>
     <t>Player</t>
   </si>
@@ -42,6 +42,9 @@
     <t>Ashu</t>
   </si>
   <si>
+    <t>Himadri</t>
+  </si>
+  <si>
     <t>Laakha</t>
   </si>
   <si>
@@ -57,6 +60,9 @@
     <t>TenWall</t>
   </si>
   <si>
+    <t>Vimal</t>
+  </si>
+  <si>
     <t>Yogi</t>
   </si>
   <si>
@@ -84,15 +90,144 @@
     <t>Points</t>
   </si>
   <si>
+    <t>South Africa vs Canada</t>
+  </si>
+  <si>
+    <t>28-06-26</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
+    <t>Draw</t>
+  </si>
+  <si>
+    <t>Colombia vs Portugal</t>
+  </si>
+  <si>
+    <t>27-06-26</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
+    <t>himadri</t>
+  </si>
+  <si>
+    <t>Jordan vs Argentina</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Panama vs England</t>
+  </si>
+  <si>
+    <t>England</t>
+  </si>
+  <si>
+    <t>Algeria vs Austria</t>
+  </si>
+  <si>
+    <t>Austria</t>
+  </si>
+  <si>
+    <t>Croatia vs Ghana</t>
+  </si>
+  <si>
+    <t>Croatia</t>
+  </si>
+  <si>
+    <t>Ghana</t>
+  </si>
+  <si>
+    <t>Congo DR vs Uzbekistan</t>
+  </si>
+  <si>
+    <t>Congo DR</t>
+  </si>
+  <si>
+    <t>Cabo Verde vs Saudi Arabia</t>
+  </si>
+  <si>
+    <t>26-06-26</t>
+  </si>
+  <si>
+    <t>Cabo Verde</t>
+  </si>
+  <si>
+    <t>Norway vs France</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Egypt vs IR Iran</t>
+  </si>
+  <si>
+    <t>Egypt</t>
+  </si>
+  <si>
+    <t>Uruguay vs Spain</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Paraguay vs Australia</t>
+  </si>
+  <si>
+    <t>25-06-26</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Türkiye vs USA</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>Türkiye</t>
+  </si>
+  <si>
+    <t>Japan vs Sweden</t>
+  </si>
+  <si>
+    <t>Ecuador vs Germany</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>Curaçao vs Côte d'Ivoire</t>
+  </si>
+  <si>
+    <t>Côte d'Ivoire</t>
+  </si>
+  <si>
+    <t>Tunisia vs Netherlands</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
     <t>South Africa vs Korea Republic</t>
   </si>
   <si>
     <t>24-06-26</t>
   </si>
   <si>
-    <t>Draw</t>
-  </si>
-  <si>
     <t>Bosnia &amp; Herz. vs Qatar</t>
   </si>
   <si>
@@ -129,18 +264,12 @@
     <t>Panama vs Croatia</t>
   </si>
   <si>
-    <t>Croatia</t>
-  </si>
-  <si>
     <t>France vs Iraq</t>
   </si>
   <si>
     <t>22-06-26</t>
   </si>
   <si>
-    <t>France</t>
-  </si>
-  <si>
     <t>Norway vs Senegal</t>
   </si>
   <si>
@@ -150,9 +279,6 @@
     <t>Argentina vs Austria</t>
   </si>
   <si>
-    <t>Argentina</t>
-  </si>
-  <si>
     <t>Jordan vs Algeria</t>
   </si>
   <si>
@@ -171,48 +297,30 @@
     <t>Spain vs Saudi Arabia</t>
   </si>
   <si>
-    <t>Spain</t>
-  </si>
-  <si>
     <t>Germany vs Côte d'Ivoire</t>
   </si>
   <si>
     <t>20-06-26</t>
   </si>
   <si>
-    <t>Germany</t>
-  </si>
-  <si>
     <t>Netherlands vs Sweden</t>
   </si>
   <si>
-    <t>Netherlands</t>
-  </si>
-  <si>
     <t>USA vs Australia</t>
   </si>
   <si>
     <t>19-06-26</t>
   </si>
   <si>
-    <t>USA</t>
-  </si>
-  <si>
     <t>Türkiye vs Paraguay</t>
   </si>
   <si>
-    <t>Türkiye</t>
-  </si>
-  <si>
     <t>Paraguay</t>
   </si>
   <si>
     <t>Brazil vs Haiti</t>
   </si>
   <si>
-    <t>Australia</t>
-  </si>
-  <si>
     <t>Scotland vs Morocco</t>
   </si>
   <si>
@@ -222,9 +330,6 @@
     <t>18-06-26</t>
   </si>
   <si>
-    <t>Canada</t>
-  </si>
-  <si>
     <t>Switzerland vs Bosnia &amp; Herz.</t>
   </si>
   <si>
@@ -249,13 +354,7 @@
     <t>17-06-26</t>
   </si>
   <si>
-    <t>England</t>
-  </si>
-  <si>
     <t>Portugal vs Congo DR</t>
-  </si>
-  <si>
-    <t>Portugal</t>
   </si>
   <si>
     <t>IR Iran vs New Zealand</t>
@@ -367,14 +466,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E7FD"/>
-        <bgColor rgb="FFD9E7FD"/>
+        <fgColor rgb="FF8CB5F9"/>
+        <bgColor rgb="FF8CB5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF8CB5F9"/>
-        <bgColor rgb="FF8CB5F9"/>
+        <fgColor rgb="FFD9E7FD"/>
+        <bgColor rgb="FFD9E7FD"/>
       </patternFill>
     </fill>
   </fills>
@@ -414,6 +513,29 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -428,29 +550,6 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-    </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -470,63 +569,63 @@
     <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="5" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="6" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="7" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="6" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="7" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="6" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="7" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="8" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="9" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="7" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="6" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="7" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -752,7 +851,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1">
-        <v>46198.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -786,10 +885,10 @@
         <v>330.0</v>
       </c>
       <c r="C3" s="9">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="D3" s="10">
-        <v>330.0</v>
+        <v>230.0</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -803,10 +902,10 @@
         <v>580.0</v>
       </c>
       <c r="C4" s="12">
-        <v>235.0</v>
+        <v>435.0</v>
       </c>
       <c r="D4" s="13">
-        <v>345.0</v>
+        <v>145.0</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -817,13 +916,13 @@
         <v>6</v>
       </c>
       <c r="B5" s="9">
-        <v>600.0</v>
+        <v>1190.0</v>
       </c>
       <c r="C5" s="9">
-        <v>670.0</v>
+        <v>1775.0</v>
       </c>
       <c r="D5" s="10">
-        <v>-70.0</v>
+        <v>-585.0</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
@@ -834,13 +933,13 @@
         <v>7</v>
       </c>
       <c r="B6" s="12">
-        <v>500.0</v>
+        <v>700.0</v>
       </c>
       <c r="C6" s="12">
-        <v>1230.0</v>
+        <v>1650.0</v>
       </c>
       <c r="D6" s="13">
-        <v>-730.0</v>
+        <v>-950.0</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -851,13 +950,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="9">
-        <v>500.0</v>
+        <v>450.0</v>
       </c>
       <c r="C7" s="9">
-        <v>120.0</v>
+        <v>300.0</v>
       </c>
       <c r="D7" s="10">
-        <v>380.0</v>
+        <v>150.0</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -868,13 +967,13 @@
         <v>9</v>
       </c>
       <c r="B8" s="12">
-        <v>100.0</v>
+        <v>935.0</v>
       </c>
       <c r="C8" s="12">
-        <v>100.0</v>
+        <v>220.0</v>
       </c>
       <c r="D8" s="13">
-        <v>0.0</v>
+        <v>715.0</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
@@ -884,13 +983,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="9">
-        <v>350.0</v>
+        <v>450.0</v>
       </c>
       <c r="C9" s="9">
-        <v>130.0</v>
+        <v>513.0</v>
       </c>
       <c r="D9" s="10">
-        <v>220.0</v>
+        <v>-63.0</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -901,13 +1000,13 @@
         <v>11</v>
       </c>
       <c r="B10" s="12">
-        <v>505.0</v>
+        <v>450.0</v>
       </c>
       <c r="C10" s="12">
-        <v>200.0</v>
+        <v>380.0</v>
       </c>
       <c r="D10" s="13">
-        <v>305.0</v>
+        <v>70.0</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -918,13 +1017,13 @@
         <v>12</v>
       </c>
       <c r="B11" s="9">
-        <v>1080.0</v>
+        <v>613.0</v>
       </c>
       <c r="C11" s="9">
-        <v>2060.0</v>
+        <v>200.0</v>
       </c>
       <c r="D11" s="10">
-        <v>-980.0</v>
+        <v>413.0</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
@@ -935,29 +1034,29 @@
         <v>13</v>
       </c>
       <c r="B12" s="12">
-        <v>200.0</v>
+        <v>2285.0</v>
       </c>
       <c r="C12" s="12">
-        <v>0.0</v>
+        <v>2810.0</v>
       </c>
       <c r="D12" s="13">
-        <v>200.0</v>
+        <v>-525.0</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="15">
-        <v>4745.0</v>
-      </c>
-      <c r="C13" s="15">
-        <v>4745.0</v>
-      </c>
-      <c r="D13" s="16">
+      <c r="B13" s="9">
+        <v>200.0</v>
+      </c>
+      <c r="C13" s="9">
+        <v>200.0</v>
+      </c>
+      <c r="D13" s="10">
         <v>0.0</v>
       </c>
       <c r="E13" s="4"/>
@@ -965,1179 +1064,1989 @@
       <c r="G13" s="4"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
+      <c r="A14" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="12">
+        <v>400.0</v>
+      </c>
+      <c r="C14" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="D14" s="13">
+        <v>400.0</v>
+      </c>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="18" t="s">
+      <c r="A15" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="B15" s="16">
+        <v>8583.0</v>
+      </c>
+      <c r="C15" s="16">
+        <v>8583.0</v>
+      </c>
+      <c r="D15" s="17">
+        <v>0.0</v>
+      </c>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="B18" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="C18" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="18" t="s">
+      <c r="D18" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="18" t="s">
+      <c r="E18" s="18" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="19" t="s">
+      <c r="F18" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="G18" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="19" t="s">
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="B19" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="20">
+        <v>75.0</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16" s="9">
+      <c r="G20" s="9">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="20">
         <v>100.0</v>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="G17" s="22">
-        <v>90.0</v>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="9">
-        <v>55.0</v>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="21" t="s">
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="21" t="s">
+      <c r="B22" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="21" t="s">
+      <c r="C22" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="G19" s="22">
-        <v>130.0</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="19" t="s">
+      <c r="G22" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F20" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="9">
+      <c r="G23" s="20">
+        <v>50.0</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="G24" s="9">
+        <v>50.0</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="20">
         <v>100.0</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G21" s="22">
-        <v>90.0</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G22" s="9">
-        <v>70.0</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G23" s="22">
-        <v>70.0</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G24" s="9">
-        <v>80.0</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="22" t="s">
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="B26" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G25" s="22">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D26" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="E26" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="19" t="s">
+      <c r="E26" s="21" t="s">
         <v>9</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>10</v>
       </c>
       <c r="G26" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="22" t="s">
+      <c r="A27" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="21" t="s">
+      <c r="B27" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="G27" s="22">
-        <v>40.0</v>
+      <c r="F27" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="20">
+        <v>100.0</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="E28" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="19" t="s">
-        <v>12</v>
+      <c r="A28" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>6</v>
       </c>
       <c r="G28" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="20">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="E29" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G29" s="22">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>6</v>
+      <c r="D30" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>11</v>
       </c>
       <c r="G30" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G31" s="20">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G33" s="20">
+        <v>200.0</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="21" t="s">
+      <c r="D34" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="9">
+        <v>53.0</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="21" t="s">
+      <c r="B35" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D35" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="G35" s="20">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F36" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G36" s="9">
+        <v>70.0</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="20">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="9">
+        <v>200.0</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="G39" s="20">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="E40" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="9">
+        <v>55.0</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="E31" s="21" t="s">
+      <c r="B41" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G41" s="20">
+        <v>250.0</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D42" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E42" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="F31" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" s="22">
-        <v>40.0</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G32" s="9">
-        <v>40.0</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="B33" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="21" t="s">
+      <c r="G42" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D43" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="E43" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="F33" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G33" s="22">
-        <v>200.0</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C34" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D34" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G34" s="9">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="B35" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" s="21" t="s">
+      <c r="F43" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="20">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B44" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D35" s="21" t="s">
+      <c r="C44" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E44" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F44" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" s="9">
+        <v>220.0</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B45" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="E35" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G35" s="22">
-        <v>65.0</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D36" s="19" t="s">
+      <c r="C45" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G45" s="20">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B46" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D46" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="E46" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F46" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="G46" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B47" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D47" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G47" s="20">
+        <v>85.0</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C48" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D48" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="E48" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="G48" s="9">
+        <v>120.0</v>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="E36" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="F36" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G36" s="9">
+      <c r="B49" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D49" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F49" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G49" s="20">
         <v>100.0</v>
       </c>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="B37" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="D37" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="E37" s="21" t="s">
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="D50" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E50" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F37" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G37" s="22">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="C38" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D38" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="E38" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G38" s="9">
-        <v>160.0</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="C39" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="D39" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E39" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G39" s="22">
-        <v>70.0</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B40" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D40" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="E40" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="G40" s="9">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="B41" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="C41" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="D41" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="E41" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="F41" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G41" s="22">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="B42" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C42" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="D42" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="E42" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="G42" s="9">
-        <v>50.0</v>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B43" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="C43" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="D43" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E43" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G43" s="22">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B44" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C44" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D44" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="E44" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G44" s="9">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B45" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="C45" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E45" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G45" s="22">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="B46" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="C46" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="D46" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="E46" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F46" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G46" s="9">
-        <v>55.0</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="B47" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="C47" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="D47" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="E47" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G47" s="22">
-        <v>75.0</v>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="B48" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="C48" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="D48" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="E48" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="G48" s="9">
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="B49" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="C49" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="D49" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="E49" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="G49" s="22">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B50" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="C50" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D50" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E50" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F50" s="19" t="s">
-        <v>74</v>
+      <c r="F50" s="21" t="s">
+        <v>14</v>
       </c>
       <c r="G50" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="B51" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="C51" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="E51" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="F51" s="21" t="s">
+      <c r="A51" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C51" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D51" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="E51" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F51" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G51" s="20">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C52" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="D52" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E52" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="F52" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G51" s="22">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="B52" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C52" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D52" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="E52" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="F52" s="19" t="s">
+      <c r="G52" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B53" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C53" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D53" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="E53" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G52" s="9">
-        <v>60.0</v>
-      </c>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="B53" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="C53" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="D53" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="E53" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G53" s="22">
-        <v>200.0</v>
+      <c r="F53" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G53" s="20">
+        <v>100.0</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="B54" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C54" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D54" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="E54" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" s="19" t="s">
-        <v>73</v>
+      <c r="A54" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B54" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C54" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D54" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E54" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F54" s="21" t="s">
+        <v>7</v>
       </c>
       <c r="G54" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="21" t="s">
+      <c r="A55" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B55" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C55" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="D55" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E55" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F55" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G55" s="20">
+        <v>90.0</v>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B56" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D56" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E56" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" s="9">
+        <v>55.0</v>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B57" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C57" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D57" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="E57" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G57" s="20">
+        <v>130.0</v>
+      </c>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B58" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C58" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="D58" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E58" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F58" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="B59" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C59" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D59" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="E59" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G59" s="20">
+        <v>90.0</v>
+      </c>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="B55" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="C55" s="21" t="s">
+      <c r="B60" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D55" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E55" s="21" t="s">
+      <c r="C60" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D60" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="E60" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="F60" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="G60" s="9">
+        <v>70.0</v>
+      </c>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C61" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D61" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E61" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G61" s="20">
+        <v>70.0</v>
+      </c>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B62" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="C62" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D62" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E62" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="F55" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="G55" s="22">
+      <c r="G62" s="9">
+        <v>80.0</v>
+      </c>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C63" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D63" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E63" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G63" s="20">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B64" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C64" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D64" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="E64" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G64" s="9">
         <v>100.0</v>
       </c>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="19" t="s">
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B65" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C65" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D65" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="E65" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G65" s="20">
+        <v>40.0</v>
+      </c>
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B66" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C66" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D66" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E66" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="B67" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="D67" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="E67" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G67" s="20">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B68" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C68" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E68" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F68" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="G68" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B69" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C69" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D69" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="E69" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F69" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G69" s="20">
+        <v>40.0</v>
+      </c>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B70" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C70" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D70" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E70" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F70" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G70" s="9">
+        <v>40.0</v>
+      </c>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B71" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="C71" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D71" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E71" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F71" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" s="20">
+        <v>200.0</v>
+      </c>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="B72" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="C72" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D72" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="E72" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F72" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="9">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B73" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C73" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D73" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E73" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="20">
+        <v>65.0</v>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="B74" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="C74" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D74" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="E74" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F74" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B75" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C75" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D75" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="E75" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F75" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G75" s="20">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="B76" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="C76" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D76" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="E76" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G76" s="9">
+        <v>160.0</v>
+      </c>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B77" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C77" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D77" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="E77" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F77" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G77" s="20">
+        <v>70.0</v>
+      </c>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B78" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="C78" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D78" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="E78" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F78" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="G78" s="9">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B79" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C79" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D79" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E79" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G79" s="20">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B80" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="C80" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D80" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="E80" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F80" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="G80" s="9">
+        <v>50.0</v>
+      </c>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B81" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C81" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D81" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="E81" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F81" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81" s="20">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B82" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="C82" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D82" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="E82" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F82" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" s="9">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="A83" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B83" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="C83" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D83" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="E83" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F83" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G83" s="20">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="A84" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B84" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="C84" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="D84" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E84" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="F84" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G84" s="9">
+        <v>55.0</v>
+      </c>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="A85" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B85" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="C85" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="B56" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D56" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="E56" s="19" t="s">
+      <c r="D85" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="E85" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="F56" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="G56" s="9">
+      <c r="F85" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G85" s="20">
+        <v>75.0</v>
+      </c>
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B86" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="C86" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="D86" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E86" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F86" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="G86" s="9">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="A87" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B87" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="C87" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D87" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="E87" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F87" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="G87" s="20">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="A88" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="B88" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="C88" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D88" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E88" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F88" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="G88" s="9">
         <v>100.0</v>
       </c>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="B57" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="C57" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="D57" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E57" s="21" t="s">
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="A89" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B89" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C89" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D89" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E89" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="F57" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G57" s="22">
+      <c r="G89" s="20">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="A90" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B90" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="C90" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D90" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E90" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="F90" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G90" s="9">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="A91" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B91" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C91" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D91" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E91" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F91" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G91" s="20">
+        <v>200.0</v>
+      </c>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B92" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="C92" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D92" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E92" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F92" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="G92" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="A93" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B93" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C93" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D93" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E93" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F93" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="G93" s="20">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="A94" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B94" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="C94" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D94" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E94" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="G94" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="A95" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="B95" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C95" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="D95" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E95" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F95" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G95" s="20">
         <v>50.0</v>
       </c>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="B58" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="C58" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D58" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="E58" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="F58" s="19" t="s">
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="A96" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="B96" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="C96" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D96" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E96" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="F96" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G58" s="9">
+      <c r="G96" s="9">
         <v>270.0</v>
       </c>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="B59" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C59" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="D59" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="E59" s="21" t="s">
+    <row r="97" ht="15.75" customHeight="1">
+      <c r="A97" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="B97" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C97" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D97" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="E97" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F59" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="G59" s="22">
+      <c r="F97" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G97" s="20">
         <v>30.0</v>
       </c>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="B60" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="C60" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D60" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="E60" s="19" t="s">
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B98" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C98" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D98" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="E98" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F60" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G60" s="9">
+      <c r="F98" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G98" s="9">
         <v>150.0</v>
       </c>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="B61" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C61" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="D61" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="E61" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="F61" s="21" t="s">
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="A99" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B99" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="C99" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D99" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="E99" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F99" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G61" s="22">
+      <c r="G99" s="20">
         <v>100.0</v>
       </c>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="B62" s="23">
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="A100" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B100" s="23">
         <v>46362.0</v>
       </c>
-      <c r="C62" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D62" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="E62" s="19" t="s">
+      <c r="C100" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D100" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E100" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="F62" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G62" s="9">
+      <c r="F100" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G100" s="9">
         <v>230.0</v>
       </c>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="B63" s="24">
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="A101" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B101" s="24">
         <v>46362.0</v>
       </c>
-      <c r="C63" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="D63" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E63" s="21" t="s">
+      <c r="C101" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D101" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="E101" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="F63" s="21" t="s">
+      <c r="F101" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G63" s="22">
+      <c r="G101" s="20">
         <v>80.0</v>
       </c>
     </row>
-    <row r="64" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
     <row r="102" ht="15.75" customHeight="1"/>
     <row r="103" ht="15.75" customHeight="1"/>
     <row r="104" ht="15.75" customHeight="1"/>
@@ -3047,6 +3956,44 @@
     <row r="1008" ht="15.75" customHeight="1"/>
     <row r="1009" ht="15.75" customHeight="1"/>
     <row r="1010" ht="15.75" customHeight="1"/>
+    <row r="1011" ht="15.75" customHeight="1"/>
+    <row r="1012" ht="15.75" customHeight="1"/>
+    <row r="1013" ht="15.75" customHeight="1"/>
+    <row r="1014" ht="15.75" customHeight="1"/>
+    <row r="1015" ht="15.75" customHeight="1"/>
+    <row r="1016" ht="15.75" customHeight="1"/>
+    <row r="1017" ht="15.75" customHeight="1"/>
+    <row r="1018" ht="15.75" customHeight="1"/>
+    <row r="1019" ht="15.75" customHeight="1"/>
+    <row r="1020" ht="15.75" customHeight="1"/>
+    <row r="1021" ht="15.75" customHeight="1"/>
+    <row r="1022" ht="15.75" customHeight="1"/>
+    <row r="1023" ht="15.75" customHeight="1"/>
+    <row r="1024" ht="15.75" customHeight="1"/>
+    <row r="1025" ht="15.75" customHeight="1"/>
+    <row r="1026" ht="15.75" customHeight="1"/>
+    <row r="1027" ht="15.75" customHeight="1"/>
+    <row r="1028" ht="15.75" customHeight="1"/>
+    <row r="1029" ht="15.75" customHeight="1"/>
+    <row r="1030" ht="15.75" customHeight="1"/>
+    <row r="1031" ht="15.75" customHeight="1"/>
+    <row r="1032" ht="15.75" customHeight="1"/>
+    <row r="1033" ht="15.75" customHeight="1"/>
+    <row r="1034" ht="15.75" customHeight="1"/>
+    <row r="1035" ht="15.75" customHeight="1"/>
+    <row r="1036" ht="15.75" customHeight="1"/>
+    <row r="1037" ht="15.75" customHeight="1"/>
+    <row r="1038" ht="15.75" customHeight="1"/>
+    <row r="1039" ht="15.75" customHeight="1"/>
+    <row r="1040" ht="15.75" customHeight="1"/>
+    <row r="1041" ht="15.75" customHeight="1"/>
+    <row r="1042" ht="15.75" customHeight="1"/>
+    <row r="1043" ht="15.75" customHeight="1"/>
+    <row r="1044" ht="15.75" customHeight="1"/>
+    <row r="1045" ht="15.75" customHeight="1"/>
+    <row r="1046" ht="15.75" customHeight="1"/>
+    <row r="1047" ht="15.75" customHeight="1"/>
+    <row r="1048" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="jS4b/Dq0CM/WvEdkf4U3k4wnEnJMQgs1O3DWezus6hk="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="2jBzE7pVM8dMVXbczc9SItoAYQHT4imvOLdmSfkmZz0="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="133">
   <si>
     <t>Player</t>
   </si>
@@ -90,6 +90,60 @@
     <t>Points</t>
   </si>
   <si>
+    <t>France vs Sweden</t>
+  </si>
+  <si>
+    <t>30-06-26</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Ivory Coast vs Norway</t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
+    <t>Mexico vs Ecuador</t>
+  </si>
+  <si>
+    <t>Mexico</t>
+  </si>
+  <si>
+    <t>Draw</t>
+  </si>
+  <si>
+    <t>Germany vs Paraguay</t>
+  </si>
+  <si>
+    <t>29-06-26</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Netherlands vs Morocco</t>
+  </si>
+  <si>
+    <t>Brazil vs Japan</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
+    <t>Morocco</t>
+  </si>
+  <si>
     <t>South Africa vs Canada</t>
   </si>
   <si>
@@ -102,9 +156,6 @@
     <t>South Africa</t>
   </si>
   <si>
-    <t>Draw</t>
-  </si>
-  <si>
     <t>Colombia vs Portugal</t>
   </si>
   <si>
@@ -162,9 +213,6 @@
     <t>Norway vs France</t>
   </si>
   <si>
-    <t>France</t>
-  </si>
-  <si>
     <t>Egypt vs IR Iran</t>
   </si>
   <si>
@@ -201,9 +249,6 @@
     <t>Ecuador vs Germany</t>
   </si>
   <si>
-    <t>Germany</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -216,12 +261,6 @@
     <t>Tunisia vs Netherlands</t>
   </si>
   <si>
-    <t>Netherlands</t>
-  </si>
-  <si>
-    <t>Japan</t>
-  </si>
-  <si>
     <t>South Africa vs Korea Republic</t>
   </si>
   <si>
@@ -237,9 +276,6 @@
     <t>Scotland vs Brazil</t>
   </si>
   <si>
-    <t>Brazil</t>
-  </si>
-  <si>
     <t>Switzerland vs Canada</t>
   </si>
   <si>
@@ -249,9 +285,6 @@
     <t>Morocco vs Haiti</t>
   </si>
   <si>
-    <t>Morocco</t>
-  </si>
-  <si>
     <t>Colombia vs Congo DR</t>
   </si>
   <si>
@@ -273,9 +306,6 @@
     <t>Norway vs Senegal</t>
   </si>
   <si>
-    <t>Norway</t>
-  </si>
-  <si>
     <t>Argentina vs Austria</t>
   </si>
   <si>
@@ -315,9 +345,6 @@
     <t>Türkiye vs Paraguay</t>
   </si>
   <si>
-    <t>Paraguay</t>
-  </si>
-  <si>
     <t>Brazil vs Haiti</t>
   </si>
   <si>
@@ -337,9 +364,6 @@
   </si>
   <si>
     <t>Mexico vs Korea Republic</t>
-  </si>
-  <si>
-    <t>Mexico</t>
   </si>
   <si>
     <t>Tenwall</t>
@@ -569,7 +593,7 @@
     <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
@@ -841,7 +865,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.75"/>
+    <col customWidth="1" min="1" max="1" width="13.38"/>
     <col customWidth="1" min="2" max="3" width="5.38"/>
     <col customWidth="1" min="4" max="4" width="6.5"/>
     <col customWidth="1" min="5" max="5" width="5.63"/>
@@ -851,7 +875,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1">
-        <v>46202.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -902,10 +926,10 @@
         <v>580.0</v>
       </c>
       <c r="C4" s="12">
-        <v>435.0</v>
+        <v>535.0</v>
       </c>
       <c r="D4" s="13">
-        <v>145.0</v>
+        <v>45.0</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -916,13 +940,13 @@
         <v>6</v>
       </c>
       <c r="B5" s="9">
-        <v>1190.0</v>
+        <v>1480.0</v>
       </c>
       <c r="C5" s="9">
-        <v>1775.0</v>
+        <v>2275.0</v>
       </c>
       <c r="D5" s="10">
-        <v>-585.0</v>
+        <v>-795.0</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
@@ -933,13 +957,13 @@
         <v>7</v>
       </c>
       <c r="B6" s="12">
-        <v>700.0</v>
+        <v>1200.0</v>
       </c>
       <c r="C6" s="12">
-        <v>1650.0</v>
+        <v>1740.0</v>
       </c>
       <c r="D6" s="13">
-        <v>-950.0</v>
+        <v>-540.0</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -950,13 +974,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="9">
-        <v>450.0</v>
+        <v>650.0</v>
       </c>
       <c r="C7" s="9">
-        <v>300.0</v>
+        <v>395.0</v>
       </c>
       <c r="D7" s="10">
-        <v>150.0</v>
+        <v>255.0</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -967,13 +991,13 @@
         <v>9</v>
       </c>
       <c r="B8" s="12">
-        <v>935.0</v>
+        <v>1120.0</v>
       </c>
       <c r="C8" s="12">
-        <v>220.0</v>
+        <v>420.0</v>
       </c>
       <c r="D8" s="13">
-        <v>715.0</v>
+        <v>700.0</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
@@ -983,13 +1007,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="9">
-        <v>450.0</v>
+        <v>600.0</v>
       </c>
       <c r="C9" s="9">
-        <v>513.0</v>
+        <v>863.0</v>
       </c>
       <c r="D9" s="10">
-        <v>-63.0</v>
+        <v>-263.0</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -1017,13 +1041,13 @@
         <v>12</v>
       </c>
       <c r="B11" s="9">
-        <v>613.0</v>
+        <v>653.0</v>
       </c>
       <c r="C11" s="9">
         <v>200.0</v>
       </c>
       <c r="D11" s="10">
-        <v>413.0</v>
+        <v>453.0</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
@@ -1034,13 +1058,13 @@
         <v>13</v>
       </c>
       <c r="B12" s="12">
-        <v>2285.0</v>
+        <v>3150.0</v>
       </c>
       <c r="C12" s="12">
-        <v>2810.0</v>
+        <v>3715.0</v>
       </c>
       <c r="D12" s="13">
-        <v>-525.0</v>
+        <v>-565.0</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -1051,13 +1075,13 @@
         <v>14</v>
       </c>
       <c r="B13" s="9">
-        <v>200.0</v>
+        <v>280.0</v>
       </c>
       <c r="C13" s="9">
-        <v>200.0</v>
+        <v>420.0</v>
       </c>
       <c r="D13" s="10">
-        <v>0.0</v>
+        <v>-140.0</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -1068,13 +1092,13 @@
         <v>15</v>
       </c>
       <c r="B14" s="12">
-        <v>400.0</v>
+        <v>550.0</v>
       </c>
       <c r="C14" s="12">
         <v>0.0</v>
       </c>
       <c r="D14" s="13">
-        <v>400.0</v>
+        <v>550.0</v>
       </c>
       <c r="E14" s="14"/>
       <c r="F14" s="14"/>
@@ -1085,10 +1109,10 @@
         <v>16</v>
       </c>
       <c r="B15" s="16">
-        <v>8583.0</v>
+        <v>11043.0</v>
       </c>
       <c r="C15" s="16">
-        <v>8583.0</v>
+        <v>11043.0</v>
       </c>
       <c r="D15" s="17">
         <v>0.0</v>
@@ -1152,67 +1176,67 @@
         <v>26</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G19" s="20">
-        <v>75.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>25</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G20" s="9">
-        <v>150.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="19" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B21" s="20" t="s">
         <v>25</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G21" s="20">
-        <v>100.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="22" t="s">
-        <v>30</v>
+        <v>27</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="C22" s="21" t="s">
         <v>31</v>
@@ -1221,10 +1245,10 @@
         <v>28</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G22" s="9">
         <v>100.0</v>
@@ -1232,183 +1256,183 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="19" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B23" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>34</v>
-      </c>
       <c r="E23" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G23" s="20">
-        <v>50.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="21" t="s">
-        <v>36</v>
-      </c>
       <c r="D24" s="21" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E24" s="21" t="s">
         <v>9</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G24" s="9">
-        <v>50.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="19" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E25" s="19" t="s">
         <v>13</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G25" s="20">
-        <v>100.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="22" t="s">
-        <v>30</v>
+        <v>27</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="C26" s="21" t="s">
         <v>28</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F26" s="21" t="s">
         <v>10</v>
       </c>
       <c r="G26" s="9">
-        <v>100.0</v>
+        <v>160.0</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="19" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F27" s="19" t="s">
         <v>13</v>
       </c>
       <c r="G27" s="20">
-        <v>100.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="22" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F28" s="21" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G28" s="9">
-        <v>100.0</v>
+        <v>400.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G29" s="20">
-        <v>150.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="22" t="s">
-        <v>30</v>
+        <v>36</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G30" s="9">
         <v>100.0</v>
@@ -1416,19 +1440,19 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C31" s="19" t="s">
         <v>38</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F31" s="19" t="s">
         <v>6</v>
@@ -1439,91 +1463,91 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="22" t="s">
-        <v>30</v>
+        <v>36</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G32" s="9">
-        <v>100.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="19" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G33" s="20">
-        <v>200.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="22" t="s">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F34" s="21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G34" s="9">
-        <v>53.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="19" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G35" s="20">
         <v>100.0</v>
@@ -1531,183 +1555,183 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="B36" s="22" t="s">
-        <v>45</v>
+        <v>35</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="E36" s="21" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F36" s="21" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G36" s="9">
-        <v>70.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="19" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G37" s="20">
-        <v>60.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="B38" s="22" t="s">
-        <v>45</v>
+        <v>35</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F38" s="21" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G38" s="9">
-        <v>200.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="19" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="E39" s="19" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G39" s="20">
-        <v>150.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="B40" s="22" t="s">
-        <v>45</v>
+        <v>36</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="E40" s="21" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F40" s="21" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G40" s="9">
-        <v>55.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>28</v>
-      </c>
       <c r="D41" s="19" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G41" s="20">
-        <v>250.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="21" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="E42" s="21" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G42" s="9">
-        <v>100.0</v>
+        <v>150.0</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="19" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G43" s="20">
         <v>100.0</v>
@@ -1715,117 +1739,117 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="21" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E44" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F44" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F44" s="21" t="s">
-        <v>13</v>
-      </c>
       <c r="G44" s="9">
-        <v>220.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="19" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E45" s="19" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F45" s="19" t="s">
         <v>6</v>
       </c>
       <c r="G45" s="20">
-        <v>100.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="21" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E46" s="21" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F46" s="21" t="s">
         <v>6</v>
       </c>
       <c r="G46" s="9">
-        <v>100.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="19" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="E47" s="19" t="s">
         <v>13</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G47" s="20">
-        <v>85.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="21" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B48" s="22" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="D48" s="21" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E48" s="21" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F48" s="21" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G48" s="9">
-        <v>120.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
@@ -1833,19 +1857,19 @@
         <v>56</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C49" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D49" s="19" t="s">
         <v>57</v>
-      </c>
-      <c r="D49" s="19" t="s">
-        <v>58</v>
       </c>
       <c r="E49" s="19" t="s">
         <v>6</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G49" s="20">
         <v>100.0</v>
@@ -1853,22 +1877,22 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="21" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="E50" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" s="21" t="s">
         <v>6</v>
-      </c>
-      <c r="F50" s="21" t="s">
-        <v>14</v>
       </c>
       <c r="G50" s="9">
         <v>100.0</v>
@@ -1876,45 +1900,45 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="19" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G51" s="20">
-        <v>100.0</v>
+        <v>150.0</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="21" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B52" s="22" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="E52" s="21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F52" s="21" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G52" s="9">
         <v>100.0</v>
@@ -1922,22 +1946,22 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="19" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G53" s="20">
         <v>100.0</v>
@@ -1945,22 +1969,22 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="21" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="E54" s="21" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F54" s="21" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G54" s="9">
         <v>100.0</v>
@@ -1968,229 +1992,229 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="19" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="E55" s="19" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G55" s="20">
-        <v>90.0</v>
+        <v>200.0</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="21" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="B56" s="22" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E56" s="21" t="s">
         <v>12</v>
       </c>
       <c r="F56" s="21" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G56" s="9">
-        <v>55.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="19" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="B57" s="20" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G57" s="20">
-        <v>130.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="21" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B58" s="22" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E58" s="21" t="s">
         <v>6</v>
       </c>
       <c r="F58" s="21" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G58" s="9">
-        <v>100.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="19" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="E59" s="19" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G59" s="20">
-        <v>90.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="21" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="B60" s="22" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="E60" s="21" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F60" s="21" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G60" s="9">
-        <v>70.0</v>
+        <v>200.0</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="19" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B61" s="20" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E61" s="19" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G61" s="20">
-        <v>70.0</v>
+        <v>150.0</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="21" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="B62" s="22" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="E62" s="21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F62" s="21" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G62" s="9">
-        <v>80.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="19" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="B63" s="20" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G63" s="20">
-        <v>15.0</v>
+        <v>250.0</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="21" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="B64" s="22" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="D64" s="21" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="E64" s="21" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F64" s="21" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G64" s="9">
         <v>100.0</v>
@@ -2198,62 +2222,62 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="19" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="B65" s="20" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G65" s="20">
-        <v>40.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="21" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="B66" s="22" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="E66" s="21" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F66" s="21" t="s">
         <v>13</v>
       </c>
       <c r="G66" s="9">
-        <v>100.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="19" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B67" s="20" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E67" s="19" t="s">
         <v>13</v>
@@ -2267,19 +2291,19 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="21" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B68" s="22" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="E68" s="21" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F68" s="21" t="s">
         <v>6</v>
@@ -2290,137 +2314,137 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="19" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B69" s="20" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F69" s="19" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G69" s="20">
-        <v>40.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="21" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B70" s="22" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D70" s="21" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E70" s="21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F70" s="21" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G70" s="9">
-        <v>40.0</v>
+        <v>120.0</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="19" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="B71" s="20" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="E71" s="19" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G71" s="20">
-        <v>200.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="21" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="B72" s="22" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C72" s="21" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="E72" s="21" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F72" s="21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G72" s="9">
-        <v>60.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="19" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="B73" s="20" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E73" s="19" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G73" s="20">
-        <v>65.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="21" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="B74" s="22" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="C74" s="21" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D74" s="21" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="E74" s="21" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F74" s="21" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G74" s="9">
         <v>100.0</v>
@@ -2428,22 +2452,22 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="19" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="B75" s="20" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E75" s="19" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F75" s="19" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G75" s="20">
         <v>100.0</v>
@@ -2451,298 +2475,298 @@
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="21" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B76" s="22" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="D76" s="21" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="E76" s="21" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F76" s="21" t="s">
         <v>7</v>
       </c>
       <c r="G76" s="9">
-        <v>160.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="19" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="B77" s="20" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="E77" s="19" t="s">
         <v>5</v>
       </c>
       <c r="F77" s="19" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G77" s="20">
-        <v>70.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="21" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="B78" s="22" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="E78" s="21" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F78" s="21" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G78" s="9">
-        <v>150.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="19" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="B79" s="20" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E79" s="19" t="s">
         <v>13</v>
       </c>
       <c r="F79" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G79" s="20">
-        <v>100.0</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="21" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="B80" s="22" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="D80" s="21" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="E80" s="21" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F80" s="21" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G80" s="9">
-        <v>50.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="19" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="B81" s="20" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F81" s="19" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G81" s="20">
-        <v>100.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="21" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B82" s="22" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="D82" s="21" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E82" s="21" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F82" s="21" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G82" s="9">
-        <v>150.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="19" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B83" s="20" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="D83" s="19" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F83" s="19" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G83" s="20">
-        <v>100.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="21" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B84" s="22" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="C84" s="21" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="D84" s="21" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="E84" s="21" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F84" s="21" t="s">
         <v>7</v>
       </c>
       <c r="G84" s="9">
-        <v>55.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="19" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B85" s="20" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="D85" s="19" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="E85" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F85" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="F85" s="19" t="s">
-        <v>7</v>
-      </c>
       <c r="G85" s="20">
-        <v>75.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="21" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B86" s="22" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="D86" s="21" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E86" s="21" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F86" s="21" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G86" s="9">
-        <v>20.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="19" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B87" s="20" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="D87" s="19" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
       <c r="E87" s="19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F87" s="19" t="s">
-        <v>108</v>
+        <v>6</v>
       </c>
       <c r="G87" s="20">
-        <v>150.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="21" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B88" s="22" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C88" s="21" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D88" s="21" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="E88" s="21" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F88" s="21" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="G88" s="9">
         <v>100.0</v>
@@ -2750,325 +2774,809 @@
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="19" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="B89" s="20" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D89" s="19" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E89" s="19" t="s">
         <v>13</v>
       </c>
       <c r="F89" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G89" s="20">
-        <v>150.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="21" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B90" s="22" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D90" s="21" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E90" s="21" t="s">
-        <v>109</v>
+        <v>4</v>
       </c>
       <c r="F90" s="21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G90" s="9">
-        <v>60.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="19" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B91" s="20" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="D91" s="19" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E91" s="19" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F91" s="19" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G91" s="20">
-        <v>200.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="21" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B92" s="22" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="C92" s="21" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D92" s="21" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E92" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F92" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="F92" s="21" t="s">
-        <v>108</v>
-      </c>
       <c r="G92" s="9">
-        <v>100.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="19" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="B93" s="20" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>31</v>
+        <v>101</v>
       </c>
       <c r="D93" s="19" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E93" s="19" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F93" s="19" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="G93" s="20">
-        <v>100.0</v>
+        <v>200.0</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="21" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B94" s="22" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C94" s="21" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D94" s="21" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E94" s="21" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F94" s="21" t="s">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="G94" s="9">
-        <v>100.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="19" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B95" s="20" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>115</v>
+        <v>34</v>
       </c>
       <c r="D95" s="19" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E95" s="19" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F95" s="19" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G95" s="20">
-        <v>50.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="21" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="B96" s="22" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D96" s="21" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E96" s="21" t="s">
-        <v>109</v>
+        <v>4</v>
       </c>
       <c r="F96" s="21" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G96" s="9">
-        <v>270.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="19" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="B97" s="20" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D97" s="19" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E97" s="19" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F97" s="19" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G97" s="20">
-        <v>30.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="21" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="B98" s="22" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D98" s="21" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E98" s="21" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F98" s="21" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G98" s="9">
-        <v>150.0</v>
+        <v>160.0</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="19" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="B99" s="20" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D99" s="19" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="E99" s="19" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F99" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G99" s="20">
-        <v>100.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="B100" s="23">
-        <v>46362.0</v>
+        <v>108</v>
+      </c>
+      <c r="B100" s="22" t="s">
+        <v>107</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="D100" s="21" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E100" s="21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F100" s="21" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G100" s="9">
-        <v>230.0</v>
+        <v>150.0</v>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="B101" s="24">
-        <v>46362.0</v>
+        <v>109</v>
+      </c>
+      <c r="B101" s="20" t="s">
+        <v>107</v>
       </c>
       <c r="C101" s="19" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="D101" s="19" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="E101" s="19" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F101" s="19" t="s">
         <v>7</v>
       </c>
       <c r="G101" s="20">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="A102" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B102" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C102" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="D102" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E102" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F102" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="G102" s="9">
+        <v>50.0</v>
+      </c>
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="A103" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B103" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="C103" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D103" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E103" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F103" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G103" s="20">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="A104" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B104" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C104" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D104" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E104" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F104" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G104" s="9">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="A105" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B105" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="C105" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D105" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E105" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F105" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G105" s="20">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="A106" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="B106" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="C106" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D106" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E106" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="F106" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G106" s="9">
+        <v>55.0</v>
+      </c>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="A107" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="B107" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="C107" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="D107" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E107" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F107" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G107" s="20">
+        <v>75.0</v>
+      </c>
+    </row>
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="A108" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="B108" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="C108" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="D108" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E108" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F108" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="G108" s="9">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="A109" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B109" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="C109" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D109" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E109" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F109" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="G109" s="20">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="A110" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B110" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="C110" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D110" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E110" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F110" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="G110" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="A111" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="B111" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C111" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D111" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E111" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F111" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G111" s="20">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="A112" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B112" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="C112" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D112" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="E112" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="F112" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G112" s="9">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="113" ht="15.75" customHeight="1">
+      <c r="A113" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="B113" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C113" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D113" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E113" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F113" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G113" s="20">
+        <v>200.0</v>
+      </c>
+    </row>
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="A114" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B114" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="C114" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D114" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="E114" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F114" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="G114" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="A115" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B115" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C115" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D115" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E115" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F115" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="G115" s="20">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="A116" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B116" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="C116" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D116" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="E116" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="F116" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="G116" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="A117" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="B117" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="C117" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="D117" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E117" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F117" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G117" s="20">
+        <v>50.0</v>
+      </c>
+    </row>
+    <row r="118" ht="15.75" customHeight="1">
+      <c r="A118" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B118" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="C118" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D118" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E118" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="F118" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G118" s="9">
+        <v>270.0</v>
+      </c>
+    </row>
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="A119" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="B119" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="C119" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D119" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="E119" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F119" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G119" s="20">
+        <v>30.0</v>
+      </c>
+    </row>
+    <row r="120" ht="15.75" customHeight="1">
+      <c r="A120" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="B120" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="C120" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D120" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E120" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F120" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G120" s="9">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="121" ht="15.75" customHeight="1">
+      <c r="A121" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B121" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="C121" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D121" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E121" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F121" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G121" s="20">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="122" ht="15.75" customHeight="1">
+      <c r="A122" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B122" s="23">
+        <v>46362.0</v>
+      </c>
+      <c r="C122" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D122" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E122" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F122" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G122" s="9">
+        <v>230.0</v>
+      </c>
+    </row>
+    <row r="123" ht="15.75" customHeight="1">
+      <c r="A123" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B123" s="24">
+        <v>46362.0</v>
+      </c>
+      <c r="C123" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D123" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E123" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F123" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G123" s="20">
         <v>80.0</v>
       </c>
     </row>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
     <row r="124" ht="15.75" customHeight="1"/>
     <row r="125" ht="15.75" customHeight="1"/>
     <row r="126" ht="15.75" customHeight="1"/>
@@ -3994,6 +4502,28 @@
     <row r="1046" ht="15.75" customHeight="1"/>
     <row r="1047" ht="15.75" customHeight="1"/>
     <row r="1048" ht="15.75" customHeight="1"/>
+    <row r="1049" ht="15.75" customHeight="1"/>
+    <row r="1050" ht="15.75" customHeight="1"/>
+    <row r="1051" ht="15.75" customHeight="1"/>
+    <row r="1052" ht="15.75" customHeight="1"/>
+    <row r="1053" ht="15.75" customHeight="1"/>
+    <row r="1054" ht="15.75" customHeight="1"/>
+    <row r="1055" ht="15.75" customHeight="1"/>
+    <row r="1056" ht="15.75" customHeight="1"/>
+    <row r="1057" ht="15.75" customHeight="1"/>
+    <row r="1058" ht="15.75" customHeight="1"/>
+    <row r="1059" ht="15.75" customHeight="1"/>
+    <row r="1060" ht="15.75" customHeight="1"/>
+    <row r="1061" ht="15.75" customHeight="1"/>
+    <row r="1062" ht="15.75" customHeight="1"/>
+    <row r="1063" ht="15.75" customHeight="1"/>
+    <row r="1064" ht="15.75" customHeight="1"/>
+    <row r="1065" ht="15.75" customHeight="1"/>
+    <row r="1066" ht="15.75" customHeight="1"/>
+    <row r="1067" ht="15.75" customHeight="1"/>
+    <row r="1068" ht="15.75" customHeight="1"/>
+    <row r="1069" ht="15.75" customHeight="1"/>
+    <row r="1070" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="138">
   <si>
     <t>Player</t>
   </si>
@@ -54,87 +54,114 @@
     <t>Mantekwal</t>
   </si>
   <si>
+    <t>Peteza</t>
+  </si>
+  <si>
+    <t>TenWall</t>
+  </si>
+  <si>
+    <t>Vimal</t>
+  </si>
+  <si>
+    <t>Yogi</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Match</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Prediction</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Winner</t>
+  </si>
+  <si>
+    <t>Loser</t>
+  </si>
+  <si>
+    <t>Points</t>
+  </si>
+  <si>
+    <t>USA vs Bosnia and Herzegovina</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>Belgium vs Senegal</t>
+  </si>
+  <si>
+    <t>Senegal</t>
+  </si>
+  <si>
+    <t>Draw</t>
+  </si>
+  <si>
+    <t>England vs Congo DR</t>
+  </si>
+  <si>
+    <t>England</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>Congo DR</t>
+  </si>
+  <si>
+    <t>France vs Sweden</t>
+  </si>
+  <si>
+    <t>30-06-26</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Ivory Coast vs Norway</t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
+    <t>Mexico vs Ecuador</t>
+  </si>
+  <si>
+    <t>Mexico</t>
+  </si>
+  <si>
+    <t>Germany vs Paraguay</t>
+  </si>
+  <si>
+    <t>29-06-26</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Netherlands vs Morocco</t>
+  </si>
+  <si>
+    <t>Brazil vs Japan</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
     <t>Peterza</t>
   </si>
   <si>
-    <t>TenWall</t>
-  </si>
-  <si>
-    <t>Vimal</t>
-  </si>
-  <si>
-    <t>Yogi</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Match</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Prediction</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Winner</t>
-  </si>
-  <si>
-    <t>Loser</t>
-  </si>
-  <si>
-    <t>Points</t>
-  </si>
-  <si>
-    <t>France vs Sweden</t>
-  </si>
-  <si>
-    <t>30-06-26</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t>Ivory Coast vs Norway</t>
-  </si>
-  <si>
-    <t>Norway</t>
-  </si>
-  <si>
-    <t>Mexico vs Ecuador</t>
-  </si>
-  <si>
-    <t>Mexico</t>
-  </si>
-  <si>
-    <t>Draw</t>
-  </si>
-  <si>
-    <t>Germany vs Paraguay</t>
-  </si>
-  <si>
-    <t>29-06-26</t>
-  </si>
-  <si>
-    <t>Germany</t>
-  </si>
-  <si>
-    <t>Netherlands vs Morocco</t>
-  </si>
-  <si>
-    <t>Brazil vs Japan</t>
-  </si>
-  <si>
-    <t>Brazil</t>
-  </si>
-  <si>
-    <t>Japan</t>
-  </si>
-  <si>
     <t>Netherlands</t>
   </si>
   <si>
@@ -177,9 +204,6 @@
     <t>Panama vs England</t>
   </si>
   <si>
-    <t>England</t>
-  </si>
-  <si>
     <t>Algeria vs Austria</t>
   </si>
   <si>
@@ -198,9 +222,6 @@
     <t>Congo DR vs Uzbekistan</t>
   </si>
   <si>
-    <t>Congo DR</t>
-  </si>
-  <si>
     <t>Cabo Verde vs Saudi Arabia</t>
   </si>
   <si>
@@ -237,9 +258,6 @@
     <t>Türkiye vs USA</t>
   </si>
   <si>
-    <t>USA</t>
-  </si>
-  <si>
     <t>Türkiye</t>
   </si>
   <si>
@@ -367,9 +385,6 @@
   </si>
   <si>
     <t>Tenwall</t>
-  </si>
-  <si>
-    <t>Peteza</t>
   </si>
   <si>
     <t>England vs Croatia</t>
@@ -457,7 +472,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -488,20 +503,8 @@
         <bgColor rgb="FF9BC2E6"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8CB5F9"/>
-        <bgColor rgb="FF8CB5F9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E7FD"/>
-        <bgColor rgb="FFD9E7FD"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border/>
     <border>
       <left style="thin">
@@ -532,6 +535,27 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
     </border>
     <border>
       <left style="thin">
@@ -582,7 +606,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -595,61 +619,55 @@
     <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="5" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="4" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="6" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="7" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="4" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="7" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="7" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="8" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="11" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="9" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="12" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="7" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="6" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="5" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -875,7 +893,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1">
-        <v>46204.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -909,10 +927,10 @@
         <v>330.0</v>
       </c>
       <c r="C3" s="9">
-        <v>100.0</v>
+        <v>200.0</v>
       </c>
       <c r="D3" s="10">
-        <v>230.0</v>
+        <v>130.0</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -940,13 +958,13 @@
         <v>6</v>
       </c>
       <c r="B5" s="9">
-        <v>1480.0</v>
+        <v>1545.0</v>
       </c>
       <c r="C5" s="9">
-        <v>2275.0</v>
+        <v>2600.0</v>
       </c>
       <c r="D5" s="10">
-        <v>-795.0</v>
+        <v>-1055.0</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
@@ -957,13 +975,13 @@
         <v>7</v>
       </c>
       <c r="B6" s="12">
-        <v>1200.0</v>
+        <v>1300.0</v>
       </c>
       <c r="C6" s="12">
-        <v>1740.0</v>
+        <v>1940.0</v>
       </c>
       <c r="D6" s="13">
-        <v>-540.0</v>
+        <v>-640.0</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -977,10 +995,10 @@
         <v>650.0</v>
       </c>
       <c r="C7" s="9">
-        <v>395.0</v>
+        <v>545.0</v>
       </c>
       <c r="D7" s="10">
-        <v>255.0</v>
+        <v>105.0</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -991,13 +1009,13 @@
         <v>9</v>
       </c>
       <c r="B8" s="12">
-        <v>1120.0</v>
+        <v>1220.0</v>
       </c>
       <c r="C8" s="12">
-        <v>420.0</v>
+        <v>435.0</v>
       </c>
       <c r="D8" s="13">
-        <v>700.0</v>
+        <v>785.0</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
@@ -1007,13 +1025,13 @@
         <v>10</v>
       </c>
       <c r="B9" s="9">
-        <v>600.0</v>
+        <v>800.0</v>
       </c>
       <c r="C9" s="9">
-        <v>863.0</v>
+        <v>928.0</v>
       </c>
       <c r="D9" s="10">
-        <v>-263.0</v>
+        <v>-128.0</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -1044,10 +1062,10 @@
         <v>653.0</v>
       </c>
       <c r="C11" s="9">
-        <v>200.0</v>
+        <v>228.0</v>
       </c>
       <c r="D11" s="10">
-        <v>453.0</v>
+        <v>425.0</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
@@ -1058,13 +1076,13 @@
         <v>13</v>
       </c>
       <c r="B12" s="12">
-        <v>3150.0</v>
+        <v>3715.0</v>
       </c>
       <c r="C12" s="12">
-        <v>3715.0</v>
+        <v>3865.0</v>
       </c>
       <c r="D12" s="13">
-        <v>-565.0</v>
+        <v>-150.0</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -1075,13 +1093,13 @@
         <v>14</v>
       </c>
       <c r="B13" s="9">
-        <v>280.0</v>
+        <v>308.0</v>
       </c>
       <c r="C13" s="9">
-        <v>420.0</v>
+        <v>510.0</v>
       </c>
       <c r="D13" s="10">
-        <v>-140.0</v>
+        <v>-202.0</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -1092,13 +1110,13 @@
         <v>15</v>
       </c>
       <c r="B14" s="12">
-        <v>550.0</v>
+        <v>615.0</v>
       </c>
       <c r="C14" s="12">
         <v>0.0</v>
       </c>
       <c r="D14" s="13">
-        <v>550.0</v>
+        <v>615.0</v>
       </c>
       <c r="E14" s="14"/>
       <c r="F14" s="14"/>
@@ -1109,10 +1127,10 @@
         <v>16</v>
       </c>
       <c r="B15" s="16">
-        <v>11043.0</v>
+        <v>12166.0</v>
       </c>
       <c r="C15" s="16">
-        <v>11043.0</v>
+        <v>12166.0</v>
       </c>
       <c r="D15" s="17">
         <v>0.0</v>
@@ -1166,54 +1184,54 @@
       <c r="A19" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="20">
+        <v>46029.0</v>
+      </c>
+      <c r="C19" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="19" t="s">
-        <v>26</v>
-      </c>
       <c r="D19" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="20">
-        <v>100.0</v>
+        <v>13</v>
+      </c>
+      <c r="G19" s="9">
+        <v>50.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="22">
+        <v>46029.0</v>
+      </c>
+      <c r="C20" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>28</v>
-      </c>
       <c r="D20" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="9">
-        <v>100.0</v>
+      <c r="G20" s="12">
+        <v>150.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="20" t="s">
-        <v>25</v>
+      <c r="B21" s="20">
+        <v>46029.0</v>
       </c>
       <c r="C21" s="19" t="s">
         <v>30</v>
@@ -1222,234 +1240,234 @@
         <v>30</v>
       </c>
       <c r="E21" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F21" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="20">
-        <v>90.0</v>
+      <c r="G21" s="9">
+        <v>125.0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="22">
+        <v>46029.0</v>
+      </c>
+      <c r="C22" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="21" t="s">
-        <v>31</v>
-      </c>
       <c r="D22" s="21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E22" s="21" t="s">
         <v>6</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="9">
-        <v>100.0</v>
+        <v>10</v>
+      </c>
+      <c r="G22" s="12">
+        <v>65.0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="20" t="s">
-        <v>25</v>
+      <c r="B23" s="20">
+        <v>46029.0</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D23" s="19" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="20">
-        <v>100.0</v>
+        <v>12</v>
+      </c>
+      <c r="G23" s="9">
+        <v>28.0</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="B24" s="22">
+        <v>46029.0</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="9">
-        <v>85.0</v>
+        <v>4</v>
+      </c>
+      <c r="G24" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="B25" s="20">
+        <v>46029.0</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E25" s="19" t="s">
         <v>13</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G25" s="20">
+        <v>14</v>
+      </c>
+      <c r="G25" s="9">
         <v>90.0</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="22">
+        <v>46029.0</v>
+      </c>
+      <c r="C26" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>28</v>
-      </c>
       <c r="D26" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26" s="9">
-        <v>160.0</v>
+        <v>13</v>
+      </c>
+      <c r="G26" s="12">
+        <v>50.0</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="B27" s="20">
+        <v>46029.0</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="20">
-        <v>30.0</v>
+        <v>7</v>
+      </c>
+      <c r="G27" s="9">
+        <v>200.0</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="22">
+        <v>46029.0</v>
+      </c>
+      <c r="C28" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>34</v>
-      </c>
       <c r="D28" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F28" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="9">
-        <v>400.0</v>
+        <v>9</v>
+      </c>
+      <c r="G28" s="12">
+        <v>15.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>33</v>
+        <v>26</v>
+      </c>
+      <c r="B29" s="20">
+        <v>46029.0</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29" s="20">
-        <v>220.0</v>
+        <v>13</v>
+      </c>
+      <c r="G29" s="9">
+        <v>50.0</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
+      </c>
+      <c r="B30" s="22">
+        <v>46029.0</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F30" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="12">
         <v>100.0</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>33</v>
+        <v>26</v>
+      </c>
+      <c r="B31" s="20">
+        <v>46029.0</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E31" s="19" t="s">
         <v>7</v>
@@ -1457,169 +1475,169 @@
       <c r="F31" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="G31" s="20">
+      <c r="G31" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32" s="9" t="s">
         <v>33</v>
       </c>
+      <c r="B32" s="22" t="s">
+        <v>34</v>
+      </c>
       <c r="C32" s="21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" s="9">
-        <v>40.0</v>
+        <v>10</v>
+      </c>
+      <c r="G32" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="G33" s="20">
+        <v>13</v>
+      </c>
+      <c r="G33" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>33</v>
+        <v>38</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>34</v>
       </c>
       <c r="C34" s="21" t="s">
         <v>39</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F34" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="G34" s="9">
-        <v>100.0</v>
+        <v>10</v>
+      </c>
+      <c r="G34" s="12">
+        <v>90.0</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G35" s="20">
+        <v>13</v>
+      </c>
+      <c r="G35" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>33</v>
+        <v>38</v>
+      </c>
+      <c r="B36" s="22" t="s">
+        <v>34</v>
       </c>
       <c r="C36" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="D36" s="21" t="s">
-        <v>31</v>
-      </c>
       <c r="E36" s="21" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F36" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G36" s="9">
+        <v>13</v>
+      </c>
+      <c r="G36" s="12">
         <v>100.0</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="19" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F37" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="G37" s="20">
-        <v>50.0</v>
+      <c r="G37" s="9">
+        <v>85.0</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B38" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C38" s="21" t="s">
-        <v>41</v>
-      </c>
       <c r="D38" s="21" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F38" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G38" s="9">
-        <v>100.0</v>
+        <v>7</v>
+      </c>
+      <c r="G38" s="12">
+        <v>90.0</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
@@ -1627,551 +1645,551 @@
         <v>36</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D39" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E39" s="19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G39" s="20">
-        <v>50.0</v>
+        <v>10</v>
+      </c>
+      <c r="G39" s="9">
+        <v>160.0</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B40" s="9" t="s">
         <v>33</v>
       </c>
+      <c r="B40" s="22" t="s">
+        <v>34</v>
+      </c>
       <c r="C40" s="21" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E40" s="21" t="s">
         <v>14</v>
       </c>
       <c r="F40" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G40" s="9">
-        <v>50.0</v>
+        <v>13</v>
+      </c>
+      <c r="G40" s="12">
+        <v>30.0</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B41" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>44</v>
-      </c>
       <c r="D41" s="19" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F41" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="G41" s="20">
-        <v>75.0</v>
+      <c r="G41" s="9">
+        <v>400.0</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E42" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="G42" s="9">
-        <v>150.0</v>
+        <v>14</v>
+      </c>
+      <c r="G42" s="12">
+        <v>220.0</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G43" s="20">
+        <v>6</v>
+      </c>
+      <c r="G43" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="C44" s="21" t="s">
-        <v>48</v>
-      </c>
       <c r="D44" s="21" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E44" s="21" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="F44" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="G44" s="9">
+      <c r="G44" s="12">
         <v>100.0</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="19" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B45" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E45" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="C45" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D45" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="E45" s="19" t="s">
-        <v>9</v>
-      </c>
       <c r="F45" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G45" s="20">
-        <v>50.0</v>
+        <v>13</v>
+      </c>
+      <c r="G45" s="9">
+        <v>40.0</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="21" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="E46" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="F46" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G46" s="9">
-        <v>50.0</v>
+      <c r="G46" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="19" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E47" s="19" t="s">
         <v>13</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G47" s="20">
+        <v>9</v>
+      </c>
+      <c r="G47" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="21" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="B48" s="22" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="D48" s="21" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="E48" s="21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F48" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G48" s="9">
+        <v>6</v>
+      </c>
+      <c r="G48" s="12">
         <v>100.0</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="19" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="E49" s="19" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" s="20">
+        <v>5</v>
+      </c>
+      <c r="G49" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="21" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F50" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G50" s="9">
-        <v>100.0</v>
+        <v>13</v>
+      </c>
+      <c r="G50" s="12">
+        <v>50.0</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="19" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G51" s="20">
-        <v>150.0</v>
+        <v>6</v>
+      </c>
+      <c r="G51" s="9">
+        <v>100.0</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="21" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B52" s="22" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E52" s="21" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F52" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G52" s="9">
-        <v>100.0</v>
+        <v>6</v>
+      </c>
+      <c r="G52" s="12">
+        <v>50.0</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="19" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F53" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="G53" s="20">
-        <v>100.0</v>
+      <c r="G53" s="9">
+        <v>50.0</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="21" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E54" s="21" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F54" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G54" s="9">
-        <v>100.0</v>
+        <v>13</v>
+      </c>
+      <c r="G54" s="12">
+        <v>75.0</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="19" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="E55" s="19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G55" s="20">
-        <v>200.0</v>
+        <v>8</v>
+      </c>
+      <c r="G55" s="9">
+        <v>150.0</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="21" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B56" s="22" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E56" s="21" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F56" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G56" s="9">
-        <v>53.0</v>
+        <v>13</v>
+      </c>
+      <c r="G56" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="19" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B57" s="20" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="G57" s="20">
+        <v>6</v>
+      </c>
+      <c r="G57" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="21" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B58" s="22" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="E58" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F58" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F58" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G58" s="9">
-        <v>70.0</v>
+      <c r="G58" s="12">
+        <v>50.0</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="19" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E59" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G59" s="20">
-        <v>60.0</v>
+        <v>6</v>
+      </c>
+      <c r="G59" s="9">
+        <v>50.0</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="21" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B60" s="22" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E60" s="21" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F60" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G60" s="9">
-        <v>200.0</v>
+        <v>10</v>
+      </c>
+      <c r="G60" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="19" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B61" s="20" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E61" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F61" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F61" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="G61" s="20">
-        <v>150.0</v>
+      <c r="G61" s="9">
+        <v>100.0</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="21" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B62" s="22" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E62" s="21" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F62" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="G62" s="9">
-        <v>55.0</v>
+      <c r="G62" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
@@ -2179,473 +2197,473 @@
         <v>61</v>
       </c>
       <c r="B63" s="20" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E63" s="19" t="s">
         <v>13</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G63" s="20">
-        <v>250.0</v>
+        <v>6</v>
+      </c>
+      <c r="G63" s="9">
+        <v>100.0</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="21" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B64" s="22" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D64" s="21" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E64" s="21" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F64" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G64" s="9">
-        <v>100.0</v>
+        <v>11</v>
+      </c>
+      <c r="G64" s="12">
+        <v>150.0</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="19" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B65" s="20" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E65" s="19" t="s">
         <v>13</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="G65" s="20">
+        <v>11</v>
+      </c>
+      <c r="G65" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="21" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="B66" s="22" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E66" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F66" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G66" s="9">
-        <v>220.0</v>
+      <c r="G66" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="19" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B67" s="20" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E67" s="19" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G67" s="20">
+        <v>10</v>
+      </c>
+      <c r="G67" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="21" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="B68" s="22" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="E68" s="21" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F68" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="G68" s="9">
-        <v>100.0</v>
+      <c r="G68" s="12">
+        <v>200.0</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="19" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B69" s="20" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="F69" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G69" s="20">
-        <v>85.0</v>
+        <v>10</v>
+      </c>
+      <c r="G69" s="9">
+        <v>53.0</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="21" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="B70" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C70" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="C70" s="21" t="s">
-        <v>39</v>
-      </c>
       <c r="D70" s="21" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E70" s="21" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F70" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G70" s="9">
-        <v>120.0</v>
+        <v>4</v>
+      </c>
+      <c r="G70" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B71" s="20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="E71" s="19" t="s">
         <v>6</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G71" s="20">
-        <v>100.0</v>
+        <v>7</v>
+      </c>
+      <c r="G71" s="9">
+        <v>70.0</v>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="21" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B72" s="22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C72" s="21" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E72" s="21" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F72" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G72" s="9">
-        <v>100.0</v>
+        <v>10</v>
+      </c>
+      <c r="G72" s="12">
+        <v>60.0</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="19" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B73" s="20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="E73" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G73" s="20">
-        <v>100.0</v>
+        <v>13</v>
+      </c>
+      <c r="G73" s="9">
+        <v>200.0</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B74" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C74" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D74" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="B74" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C74" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="D74" s="21" t="s">
-        <v>31</v>
-      </c>
       <c r="E74" s="21" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F74" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G74" s="9">
-        <v>100.0</v>
+        <v>8</v>
+      </c>
+      <c r="G74" s="12">
+        <v>150.0</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="19" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B75" s="20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E75" s="19" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="F75" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="G75" s="20">
-        <v>100.0</v>
+        <v>13</v>
+      </c>
+      <c r="G75" s="9">
+        <v>55.0</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="21" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B76" s="22" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="D76" s="21" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E76" s="21" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F76" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G76" s="9">
-        <v>100.0</v>
+      <c r="G76" s="12">
+        <v>250.0</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="19" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B77" s="20" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="E77" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F77" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="F77" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="G77" s="20">
-        <v>90.0</v>
+      <c r="G77" s="9">
+        <v>100.0</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="21" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B78" s="22" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="E78" s="21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F78" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G78" s="9">
-        <v>55.0</v>
+        <v>5</v>
+      </c>
+      <c r="G78" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="19" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B79" s="20" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="E79" s="19" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F79" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G79" s="20">
-        <v>130.0</v>
+        <v>13</v>
+      </c>
+      <c r="G79" s="9">
+        <v>220.0</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="21" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B80" s="22" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="D80" s="21" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="E80" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F80" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G80" s="9">
+      <c r="G80" s="12">
         <v>100.0</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="19" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B81" s="20" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F81" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="G81" s="20">
-        <v>90.0</v>
+      <c r="G81" s="9">
+        <v>100.0</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="21" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B82" s="22" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D82" s="21" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E82" s="21" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F82" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="G82" s="9">
-        <v>70.0</v>
+      <c r="G82" s="12">
+        <v>85.0</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B83" s="20" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="D83" s="19" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="E83" s="19" t="s">
         <v>13</v>
@@ -2653,643 +2671,643 @@
       <c r="F83" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="G83" s="20">
-        <v>70.0</v>
+      <c r="G83" s="9">
+        <v>120.0</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="21" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="B84" s="22" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C84" s="21" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="D84" s="21" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="E84" s="21" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F84" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G84" s="9">
-        <v>80.0</v>
+        <v>14</v>
+      </c>
+      <c r="G84" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="19" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B85" s="20" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D85" s="19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E85" s="19" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F85" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="G85" s="20">
-        <v>15.0</v>
+        <v>14</v>
+      </c>
+      <c r="G85" s="9">
+        <v>100.0</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="21" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="B86" s="22" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D86" s="21" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="E86" s="21" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F86" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G86" s="9">
+        <v>6</v>
+      </c>
+      <c r="G86" s="12">
         <v>100.0</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="19" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="B87" s="20" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D87" s="19" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E87" s="19" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F87" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G87" s="20">
-        <v>40.0</v>
+        <v>7</v>
+      </c>
+      <c r="G87" s="9">
+        <v>100.0</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="21" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="B88" s="22" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C88" s="21" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D88" s="21" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="E88" s="21" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F88" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G88" s="9">
+        <v>9</v>
+      </c>
+      <c r="G88" s="12">
         <v>100.0</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="19" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B89" s="20" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="D89" s="19" t="s">
         <v>28</v>
       </c>
       <c r="E89" s="19" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F89" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G89" s="20">
+        <v>7</v>
+      </c>
+      <c r="G89" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="21" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B90" s="22" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="D90" s="21" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="E90" s="21" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F90" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G90" s="9">
-        <v>100.0</v>
+        <v>9</v>
+      </c>
+      <c r="G90" s="12">
+        <v>90.0</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="19" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B91" s="20" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="D91" s="19" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E91" s="19" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="F91" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G91" s="20">
-        <v>40.0</v>
+        <v>13</v>
+      </c>
+      <c r="G91" s="9">
+        <v>55.0</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="21" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B92" s="22" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C92" s="21" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="D92" s="21" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="E92" s="21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F92" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G92" s="9">
-        <v>40.0</v>
+        <v>6</v>
+      </c>
+      <c r="G92" s="12">
+        <v>130.0</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="19" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B93" s="20" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="D93" s="19" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E93" s="19" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F93" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="G93" s="20">
-        <v>200.0</v>
+      <c r="G93" s="9">
+        <v>100.0</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="21" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B94" s="22" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="C94" s="21" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="D94" s="21" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="E94" s="21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F94" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G94" s="9">
-        <v>60.0</v>
+        <v>6</v>
+      </c>
+      <c r="G94" s="12">
+        <v>90.0</v>
       </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="19" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B95" s="20" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D95" s="19" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="E95" s="19" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F95" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G95" s="20">
-        <v>65.0</v>
+        <v>6</v>
+      </c>
+      <c r="G95" s="9">
+        <v>70.0</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="21" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B96" s="22" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="D96" s="21" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="E96" s="21" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F96" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G96" s="9">
-        <v>100.0</v>
+        <v>6</v>
+      </c>
+      <c r="G96" s="12">
+        <v>70.0</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="19" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B97" s="20" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="D97" s="19" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="E97" s="19" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F97" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G97" s="20">
-        <v>100.0</v>
+        <v>7</v>
+      </c>
+      <c r="G97" s="9">
+        <v>80.0</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="21" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B98" s="22" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D98" s="21" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E98" s="21" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="F98" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G98" s="9">
-        <v>160.0</v>
+        <v>5</v>
+      </c>
+      <c r="G98" s="12">
+        <v>15.0</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="19" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B99" s="20" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="D99" s="19" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="E99" s="19" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F99" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G99" s="20">
-        <v>70.0</v>
+        <v>10</v>
+      </c>
+      <c r="G99" s="9">
+        <v>100.0</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="21" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B100" s="22" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D100" s="21" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E100" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="F100" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F100" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G100" s="9">
-        <v>150.0</v>
+      <c r="G100" s="12">
+        <v>40.0</v>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="19" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B101" s="20" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C101" s="19" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D101" s="19" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="E101" s="19" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F101" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G101" s="20">
+        <v>13</v>
+      </c>
+      <c r="G101" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="21" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B102" s="22" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="D102" s="21" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="E102" s="21" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F102" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G102" s="9">
-        <v>50.0</v>
+        <v>6</v>
+      </c>
+      <c r="G102" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="19" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B103" s="20" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D103" s="19" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="E103" s="19" t="s">
         <v>4</v>
       </c>
       <c r="F103" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G103" s="20">
+        <v>6</v>
+      </c>
+      <c r="G103" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="21" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B104" s="22" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C104" s="21" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D104" s="21" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E104" s="21" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F104" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G104" s="9">
-        <v>150.0</v>
+        <v>11</v>
+      </c>
+      <c r="G104" s="12">
+        <v>40.0</v>
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="19" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B105" s="20" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="D105" s="19" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="E105" s="19" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F105" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G105" s="20">
-        <v>100.0</v>
+        <v>11</v>
+      </c>
+      <c r="G105" s="9">
+        <v>40.0</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="21" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B106" s="22" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C106" s="21" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="D106" s="21" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E106" s="21" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F106" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G106" s="9">
-        <v>55.0</v>
+        <v>13</v>
+      </c>
+      <c r="G106" s="12">
+        <v>200.0</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="19" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B107" s="20" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="D107" s="19" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="E107" s="19" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F107" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G107" s="20">
-        <v>75.0</v>
+        <v>13</v>
+      </c>
+      <c r="G107" s="9">
+        <v>60.0</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B108" s="22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C108" s="21" t="s">
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="D108" s="21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E108" s="21" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="F108" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G108" s="9">
-        <v>20.0</v>
+        <v>13</v>
+      </c>
+      <c r="G108" s="12">
+        <v>65.0</v>
       </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="19" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B109" s="20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D109" s="19" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="E109" s="19" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F109" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="G109" s="20">
-        <v>150.0</v>
+        <v>13</v>
+      </c>
+      <c r="G109" s="9">
+        <v>100.0</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="21" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B110" s="22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C110" s="21" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D110" s="21" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="E110" s="21" t="s">
         <v>6</v>
       </c>
       <c r="F110" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="G110" s="9">
+        <v>13</v>
+      </c>
+      <c r="G110" s="12">
         <v>100.0</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="19" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B111" s="20" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D111" s="19" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E111" s="19" t="s">
         <v>13</v>
@@ -3297,302 +3315,612 @@
       <c r="F111" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G111" s="20">
-        <v>150.0</v>
+      <c r="G111" s="9">
+        <v>160.0</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="21" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B112" s="22" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C112" s="21" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="D112" s="21" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="E112" s="21" t="s">
-        <v>117</v>
+        <v>5</v>
       </c>
       <c r="F112" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G112" s="9">
-        <v>60.0</v>
+        <v>6</v>
+      </c>
+      <c r="G112" s="12">
+        <v>70.0</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="19" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B113" s="20" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C113" s="19" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="D113" s="19" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E113" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F113" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G113" s="20">
-        <v>200.0</v>
+        <v>5</v>
+      </c>
+      <c r="G113" s="9">
+        <v>150.0</v>
       </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="21" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B114" s="22" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C114" s="21" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="D114" s="21" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E114" s="21" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F114" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="G114" s="9">
+        <v>7</v>
+      </c>
+      <c r="G114" s="12">
         <v>100.0</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="19" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B115" s="20" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C115" s="19" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="D115" s="19" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E115" s="19" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F115" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="G115" s="20">
-        <v>100.0</v>
+        <v>5</v>
+      </c>
+      <c r="G115" s="9">
+        <v>50.0</v>
       </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B116" s="22" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C116" s="21" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="D116" s="21" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E116" s="21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F116" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="G116" s="9">
+        <v>13</v>
+      </c>
+      <c r="G116" s="12">
         <v>100.0</v>
       </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="19" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B117" s="20" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="D117" s="19" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="E117" s="19" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F117" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G117" s="20">
-        <v>50.0</v>
+        <v>13</v>
+      </c>
+      <c r="G117" s="9">
+        <v>150.0</v>
       </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="21" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="B118" s="22" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C118" s="21" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D118" s="21" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="E118" s="21" t="s">
-        <v>117</v>
+        <v>7</v>
       </c>
       <c r="F118" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G118" s="9">
-        <v>270.0</v>
+        <v>13</v>
+      </c>
+      <c r="G118" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="19" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B119" s="20" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D119" s="19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E119" s="19" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F119" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="G119" s="20">
-        <v>30.0</v>
+        <v>7</v>
+      </c>
+      <c r="G119" s="9">
+        <v>55.0</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="21" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B120" s="22" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C120" s="21" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="D120" s="21" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="E120" s="21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F120" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G120" s="9">
-        <v>150.0</v>
+        <v>7</v>
+      </c>
+      <c r="G120" s="12">
+        <v>75.0</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="19" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="B121" s="20" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="C121" s="19" t="s">
-        <v>31</v>
+        <v>120</v>
       </c>
       <c r="D121" s="19" t="s">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="E121" s="19" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F121" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G121" s="20">
-        <v>100.0</v>
+        <v>5</v>
+      </c>
+      <c r="G121" s="9">
+        <v>20.0</v>
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="B122" s="23">
-        <v>46362.0</v>
+        <v>121</v>
+      </c>
+      <c r="B122" s="22" t="s">
+        <v>118</v>
       </c>
       <c r="C122" s="21" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D122" s="21" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E122" s="21" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F122" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G122" s="9">
-        <v>230.0</v>
+        <v>122</v>
+      </c>
+      <c r="G122" s="12">
+        <v>150.0</v>
       </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B123" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C123" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D123" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="E123" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F123" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G123" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="124" ht="15.75" customHeight="1">
+      <c r="A124" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B124" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="C124" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D124" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E124" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F124" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G124" s="12">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="125" ht="15.75" customHeight="1">
+      <c r="A125" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="B125" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="C125" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D125" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E125" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F125" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G125" s="9">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="126" ht="15.75" customHeight="1">
+      <c r="A126" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B126" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="C126" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D126" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E126" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F126" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G126" s="12">
+        <v>200.0</v>
+      </c>
+    </row>
+    <row r="127" ht="15.75" customHeight="1">
+      <c r="A127" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="B127" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="C127" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D127" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E127" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F127" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="G127" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="128" ht="15.75" customHeight="1">
+      <c r="A128" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B128" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="C128" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D128" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E128" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F128" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G128" s="12">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="129" ht="15.75" customHeight="1">
+      <c r="A129" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="B129" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="C129" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D129" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E129" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F129" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="G129" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="130" ht="15.75" customHeight="1">
+      <c r="A130" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="B130" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="C130" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D130" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E130" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F130" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G130" s="12">
+        <v>50.0</v>
+      </c>
+    </row>
+    <row r="131" ht="15.75" customHeight="1">
+      <c r="A131" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="B131" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C131" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D131" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E131" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F131" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G131" s="9">
+        <v>270.0</v>
+      </c>
+    </row>
+    <row r="132" ht="15.75" customHeight="1">
+      <c r="A132" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B132" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="C132" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D132" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E132" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F132" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="G132" s="12">
+        <v>30.0</v>
+      </c>
+    </row>
+    <row r="133" ht="15.75" customHeight="1">
+      <c r="A133" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="B123" s="24">
+      <c r="B133" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C133" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D133" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E133" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F133" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G133" s="9">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="134" ht="15.75" customHeight="1">
+      <c r="A134" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B134" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="C134" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D134" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="E134" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F134" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G134" s="12">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="135" ht="15.75" customHeight="1">
+      <c r="A135" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B135" s="20">
         <v>46362.0</v>
       </c>
-      <c r="C123" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="D123" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="E123" s="19" t="s">
+      <c r="C135" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D135" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E135" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F135" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G135" s="9">
+        <v>230.0</v>
+      </c>
+    </row>
+    <row r="136" ht="15.75" customHeight="1">
+      <c r="A136" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B136" s="22">
+        <v>46362.0</v>
+      </c>
+      <c r="C136" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D136" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E136" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="F123" s="19" t="s">
+      <c r="F136" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G123" s="20">
+      <c r="G136" s="12">
         <v>80.0</v>
       </c>
     </row>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1">
+      <c r="A137" s="19"/>
+      <c r="B137" s="20"/>
+      <c r="C137" s="19"/>
+      <c r="D137" s="19"/>
+      <c r="E137" s="19"/>
+      <c r="F137" s="19"/>
+      <c r="G137" s="9"/>
+    </row>
+    <row r="138" ht="15.75" customHeight="1">
+      <c r="A138" s="21"/>
+      <c r="B138" s="22"/>
+      <c r="C138" s="21"/>
+      <c r="D138" s="21"/>
+      <c r="E138" s="21"/>
+      <c r="F138" s="21"/>
+      <c r="G138" s="12"/>
+    </row>
+    <row r="139" ht="15.75" customHeight="1">
+      <c r="A139" s="19"/>
+      <c r="B139" s="20"/>
+      <c r="C139" s="19"/>
+      <c r="D139" s="19"/>
+      <c r="E139" s="19"/>
+      <c r="F139" s="19"/>
+      <c r="G139" s="9"/>
+    </row>
     <row r="140" ht="15.75" customHeight="1"/>
     <row r="141" ht="15.75" customHeight="1"/>
     <row r="142" ht="15.75" customHeight="1"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="2jBzE7pVM8dMVXbczc9SItoAYQHT4imvOLdmSfkmZz0="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="5oY9B4xJQkSqhMBp0zSbojS6FBaUYBq0Gp1IJmy2K0g="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="148">
   <si>
     <t>Player</t>
   </si>
@@ -90,6 +90,84 @@
     <t>Points</t>
   </si>
   <si>
+    <t>Mexico vs England</t>
+  </si>
+  <si>
+    <t>England</t>
+  </si>
+  <si>
+    <t>himadri</t>
+  </si>
+  <si>
+    <t>Brazil vs Norway</t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
+    <t>Paraguay vs France</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Canada vs Morocco</t>
+  </si>
+  <si>
+    <t>Morocco</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Australia vs Egypt</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Draw</t>
+  </si>
+  <si>
+    <t>Colombia vs Ghana</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>Argentina vs Cape Verde</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Egypt</t>
+  </si>
+  <si>
+    <t>Spain vs Austria</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Switzerland vs Algeria</t>
+  </si>
+  <si>
+    <t>Switzerland</t>
+  </si>
+  <si>
+    <t>Portugal vs Croatia</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
+    <t>Croatia</t>
+  </si>
+  <si>
+    <t>Algeria</t>
+  </si>
+  <si>
     <t>USA vs Bosnia and Herzegovina</t>
   </si>
   <si>
@@ -102,15 +180,9 @@
     <t>Senegal</t>
   </si>
   <si>
-    <t>Draw</t>
-  </si>
-  <si>
     <t>England vs Congo DR</t>
   </si>
   <si>
-    <t>England</t>
-  </si>
-  <si>
     <t>Belgium</t>
   </si>
   <si>
@@ -123,15 +195,9 @@
     <t>30-06-26</t>
   </si>
   <si>
-    <t>France</t>
-  </si>
-  <si>
     <t>Ivory Coast vs Norway</t>
   </si>
   <si>
-    <t>Norway</t>
-  </si>
-  <si>
     <t>Mexico vs Ecuador</t>
   </si>
   <si>
@@ -168,18 +234,12 @@
     <t>Paraguay</t>
   </si>
   <si>
-    <t>Morocco</t>
-  </si>
-  <si>
     <t>South Africa vs Canada</t>
   </si>
   <si>
     <t>28-06-26</t>
   </si>
   <si>
-    <t>Canada</t>
-  </si>
-  <si>
     <t>South Africa</t>
   </si>
   <si>
@@ -189,18 +249,9 @@
     <t>27-06-26</t>
   </si>
   <si>
-    <t>Portugal</t>
-  </si>
-  <si>
-    <t>himadri</t>
-  </si>
-  <si>
     <t>Jordan vs Argentina</t>
   </si>
   <si>
-    <t>Argentina</t>
-  </si>
-  <si>
     <t>Panama vs England</t>
   </si>
   <si>
@@ -213,9 +264,6 @@
     <t>Croatia vs Ghana</t>
   </si>
   <si>
-    <t>Croatia</t>
-  </si>
-  <si>
     <t>Ghana</t>
   </si>
   <si>
@@ -237,24 +285,15 @@
     <t>Egypt vs IR Iran</t>
   </si>
   <si>
-    <t>Egypt</t>
-  </si>
-  <si>
     <t>Uruguay vs Spain</t>
   </si>
   <si>
-    <t>Spain</t>
-  </si>
-  <si>
     <t>Paraguay vs Australia</t>
   </si>
   <si>
     <t>25-06-26</t>
   </si>
   <si>
-    <t>Australia</t>
-  </si>
-  <si>
     <t>Türkiye vs USA</t>
   </si>
   <si>
@@ -297,9 +336,6 @@
     <t>Switzerland vs Canada</t>
   </si>
   <si>
-    <t>Switzerland</t>
-  </si>
-  <si>
     <t>Morocco vs Haiti</t>
   </si>
   <si>
@@ -309,9 +345,6 @@
     <t>23-06-26</t>
   </si>
   <si>
-    <t>Colombia</t>
-  </si>
-  <si>
     <t>Panama vs Croatia</t>
   </si>
   <si>
@@ -328,9 +361,6 @@
   </si>
   <si>
     <t>Jordan vs Algeria</t>
-  </si>
-  <si>
-    <t>Algeria</t>
   </si>
   <si>
     <t>Uruguay vs Cabo Verde</t>
@@ -504,7 +534,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border/>
     <border>
       <left style="thin">
@@ -535,27 +565,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
     </border>
     <border>
       <left style="thin">
@@ -619,55 +628,55 @@
     <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="5" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="7" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="7" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="9" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="10" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="11" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="12" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -893,7 +902,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -927,10 +936,10 @@
         <v>330.0</v>
       </c>
       <c r="C3" s="9">
-        <v>200.0</v>
+        <v>280.0</v>
       </c>
       <c r="D3" s="10">
-        <v>130.0</v>
+        <v>50.0</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -941,13 +950,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="12">
-        <v>580.0</v>
+        <v>610.0</v>
       </c>
       <c r="C4" s="12">
-        <v>535.0</v>
+        <v>675.0</v>
       </c>
       <c r="D4" s="13">
-        <v>45.0</v>
+        <v>-65.0</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -958,13 +967,13 @@
         <v>6</v>
       </c>
       <c r="B5" s="9">
-        <v>1545.0</v>
+        <v>3660.0</v>
       </c>
       <c r="C5" s="9">
-        <v>2600.0</v>
+        <v>3050.0</v>
       </c>
       <c r="D5" s="10">
-        <v>-1055.0</v>
+        <v>610.0</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
@@ -975,13 +984,13 @@
         <v>7</v>
       </c>
       <c r="B6" s="12">
-        <v>1300.0</v>
+        <v>1550.0</v>
       </c>
       <c r="C6" s="12">
         <v>1940.0</v>
       </c>
       <c r="D6" s="13">
-        <v>-640.0</v>
+        <v>-390.0</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -992,13 +1001,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="9">
-        <v>650.0</v>
+        <v>1145.0</v>
       </c>
       <c r="C7" s="9">
-        <v>545.0</v>
+        <v>975.0</v>
       </c>
       <c r="D7" s="10">
-        <v>105.0</v>
+        <v>170.0</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -1009,13 +1018,13 @@
         <v>9</v>
       </c>
       <c r="B8" s="12">
-        <v>1220.0</v>
+        <v>1400.0</v>
       </c>
       <c r="C8" s="12">
-        <v>435.0</v>
+        <v>735.0</v>
       </c>
       <c r="D8" s="13">
-        <v>785.0</v>
+        <v>665.0</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
@@ -1028,10 +1037,10 @@
         <v>800.0</v>
       </c>
       <c r="C9" s="9">
-        <v>928.0</v>
+        <v>1298.0</v>
       </c>
       <c r="D9" s="10">
-        <v>-128.0</v>
+        <v>-498.0</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -1059,13 +1068,13 @@
         <v>12</v>
       </c>
       <c r="B11" s="9">
-        <v>653.0</v>
+        <v>703.0</v>
       </c>
       <c r="C11" s="9">
-        <v>228.0</v>
+        <v>408.0</v>
       </c>
       <c r="D11" s="10">
-        <v>425.0</v>
+        <v>295.0</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
@@ -1076,13 +1085,13 @@
         <v>13</v>
       </c>
       <c r="B12" s="12">
-        <v>3715.0</v>
+        <v>4265.0</v>
       </c>
       <c r="C12" s="12">
-        <v>3865.0</v>
+        <v>5585.0</v>
       </c>
       <c r="D12" s="13">
-        <v>-150.0</v>
+        <v>-1320.0</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -1110,10 +1119,10 @@
         <v>15</v>
       </c>
       <c r="B14" s="12">
-        <v>615.0</v>
+        <v>715.0</v>
       </c>
       <c r="C14" s="12">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="D14" s="13">
         <v>615.0</v>
@@ -1127,10 +1136,10 @@
         <v>16</v>
       </c>
       <c r="B15" s="16">
-        <v>12166.0</v>
+        <v>15936.0</v>
       </c>
       <c r="C15" s="16">
-        <v>12166.0</v>
+        <v>15936.0</v>
       </c>
       <c r="D15" s="17">
         <v>0.0</v>
@@ -1185,7 +1194,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="20">
-        <v>46029.0</v>
+        <v>46180.0</v>
       </c>
       <c r="C19" s="19" t="s">
         <v>25</v>
@@ -1194,59 +1203,59 @@
         <v>25</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="9">
-        <v>50.0</v>
+        <v>4</v>
+      </c>
+      <c r="G19" s="12">
+        <v>80.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="22">
-        <v>46029.0</v>
+        <v>46180.0</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="G20" s="12">
+        <v>6</v>
+      </c>
+      <c r="G20" s="9">
         <v>150.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="19" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B21" s="20">
-        <v>46029.0</v>
+        <v>46180.0</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G21" s="9">
-        <v>125.0</v>
+        <v>13</v>
+      </c>
+      <c r="G21" s="12">
+        <v>150.0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -1254,7 +1263,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="22">
-        <v>46029.0</v>
+        <v>46180.0</v>
       </c>
       <c r="C22" s="21" t="s">
         <v>25</v>
@@ -1266,10 +1275,10 @@
         <v>6</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="12">
-        <v>65.0</v>
+        <v>13</v>
+      </c>
+      <c r="G22" s="9">
+        <v>160.0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -1277,7 +1286,7 @@
         <v>29</v>
       </c>
       <c r="B23" s="20">
-        <v>46029.0</v>
+        <v>46149.0</v>
       </c>
       <c r="C23" s="19" t="s">
         <v>30</v>
@@ -1286,1591 +1295,1591 @@
         <v>30</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23" s="9">
-        <v>28.0</v>
+        <v>10</v>
+      </c>
+      <c r="G23" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B24" s="22">
-        <v>46029.0</v>
+        <v>46119.0</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="12">
-        <v>100.0</v>
+        <v>9</v>
+      </c>
+      <c r="G24" s="9">
+        <v>200.0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="19" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B25" s="20">
-        <v>46029.0</v>
+        <v>46119.0</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E25" s="19" t="s">
         <v>13</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" s="9">
-        <v>90.0</v>
+        <v>8</v>
+      </c>
+      <c r="G25" s="12">
+        <v>200.0</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="21" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B26" s="22">
-        <v>46029.0</v>
+        <v>46119.0</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" s="12">
-        <v>50.0</v>
+        <v>12</v>
+      </c>
+      <c r="G26" s="9">
+        <v>30.0</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="19" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B27" s="20">
-        <v>46029.0</v>
+        <v>46088.0</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E27" s="19" t="s">
         <v>13</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G27" s="9">
-        <v>200.0</v>
+        <v>9</v>
+      </c>
+      <c r="G27" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="21" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B28" s="22">
-        <v>46029.0</v>
+        <v>46088.0</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F28" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="G28" s="12">
-        <v>15.0</v>
+        <v>10</v>
+      </c>
+      <c r="G28" s="9">
+        <v>90.0</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="19" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B29" s="20">
-        <v>46029.0</v>
+        <v>46088.0</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" s="9">
-        <v>50.0</v>
+        <v>8</v>
+      </c>
+      <c r="G29" s="12">
+        <v>150.0</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="21" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B30" s="22">
-        <v>46029.0</v>
+        <v>46088.0</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G30" s="12">
-        <v>100.0</v>
+        <v>13</v>
+      </c>
+      <c r="G30" s="9">
+        <v>1000.0</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="19" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B31" s="20">
-        <v>46029.0</v>
+        <v>46088.0</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F31" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="12">
         <v>100.0</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32" s="22" t="s">
         <v>34</v>
       </c>
+      <c r="B32" s="22">
+        <v>46088.0</v>
+      </c>
       <c r="C32" s="21" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G32" s="12">
+        <v>15</v>
+      </c>
+      <c r="G32" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="B33" s="20">
+        <v>46088.0</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" s="9">
+        <v>6</v>
+      </c>
+      <c r="G33" s="12">
         <v>100.0</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="22" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="B34" s="22">
+        <v>46088.0</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E34" s="21" t="s">
         <v>6</v>
       </c>
       <c r="F34" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="12">
-        <v>90.0</v>
+        <v>12</v>
+      </c>
+      <c r="G34" s="9">
+        <v>100.0</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B35" s="20" t="s">
         <v>34</v>
       </c>
+      <c r="B35" s="20">
+        <v>46088.0</v>
+      </c>
       <c r="C35" s="19" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" s="9">
+        <v>6</v>
+      </c>
+      <c r="G35" s="12">
         <v>100.0</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="22" t="s">
-        <v>34</v>
+        <v>42</v>
+      </c>
+      <c r="B36" s="22">
+        <v>46060.0</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E36" s="21" t="s">
         <v>6</v>
       </c>
       <c r="F36" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="12">
+        <v>10</v>
+      </c>
+      <c r="G36" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>34</v>
+        <v>44</v>
+      </c>
+      <c r="B37" s="20">
+        <v>46060.0</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37" s="9">
-        <v>85.0</v>
+        <v>5</v>
+      </c>
+      <c r="G37" s="12">
+        <v>65.0</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B38" s="22" t="s">
-        <v>34</v>
+        <v>42</v>
+      </c>
+      <c r="B38" s="22">
+        <v>46060.0</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F38" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G38" s="12">
-        <v>90.0</v>
+        <v>13</v>
+      </c>
+      <c r="G38" s="9">
+        <v>50.0</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B39" s="20" t="s">
-        <v>34</v>
+        <v>42</v>
+      </c>
+      <c r="B39" s="20">
+        <v>46060.0</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E39" s="19" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G39" s="9">
-        <v>160.0</v>
+        <v>13</v>
+      </c>
+      <c r="G39" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B40" s="22" t="s">
-        <v>34</v>
+        <v>44</v>
+      </c>
+      <c r="B40" s="22">
+        <v>46060.0</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E40" s="21" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F40" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="12">
-        <v>30.0</v>
+        <v>5</v>
+      </c>
+      <c r="G40" s="9">
+        <v>75.0</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="20" t="s">
-        <v>41</v>
+        <v>46</v>
+      </c>
+      <c r="B41" s="20">
+        <v>46060.0</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G41" s="9">
-        <v>400.0</v>
+        <v>26</v>
+      </c>
+      <c r="G41" s="12">
+        <v>80.0</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="22" t="s">
-        <v>41</v>
+        <v>46</v>
+      </c>
+      <c r="B42" s="22">
+        <v>46060.0</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E42" s="21" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G42" s="12">
-        <v>220.0</v>
+        <v>10</v>
+      </c>
+      <c r="G42" s="9">
+        <v>80.0</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="B43" s="20" t="s">
-        <v>41</v>
+        <v>46</v>
+      </c>
+      <c r="B43" s="20">
+        <v>46060.0</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G43" s="9">
-        <v>100.0</v>
+        <v>12</v>
+      </c>
+      <c r="G43" s="12">
+        <v>50.0</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44" s="22" t="s">
-        <v>41</v>
+        <v>46</v>
+      </c>
+      <c r="B44" s="22">
+        <v>46060.0</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E44" s="21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F44" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G44" s="12">
-        <v>100.0</v>
+        <v>13</v>
+      </c>
+      <c r="G44" s="9">
+        <v>80.0</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" s="20" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="B45" s="20">
+        <v>46060.0</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E45" s="19" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="F45" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="G45" s="9">
-        <v>40.0</v>
+      <c r="G45" s="12">
+        <v>50.0</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="22" t="s">
-        <v>41</v>
+        <v>44</v>
+      </c>
+      <c r="B46" s="22">
+        <v>46060.0</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E46" s="21" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F46" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="G46" s="12">
-        <v>100.0</v>
+        <v>13</v>
+      </c>
+      <c r="G46" s="9">
+        <v>50.0</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B47" s="20" t="s">
-        <v>41</v>
+        <v>44</v>
+      </c>
+      <c r="B47" s="20">
+        <v>46060.0</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E47" s="19" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="G47" s="9">
-        <v>100.0</v>
+        <v>13</v>
+      </c>
+      <c r="G47" s="12">
+        <v>80.0</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="22" t="s">
-        <v>41</v>
+        <v>50</v>
+      </c>
+      <c r="B48" s="22">
+        <v>46029.0</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D48" s="21" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="E48" s="21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F48" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G48" s="12">
-        <v>100.0</v>
+        <v>13</v>
+      </c>
+      <c r="G48" s="9">
+        <v>50.0</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="20" t="s">
-        <v>41</v>
+        <v>52</v>
+      </c>
+      <c r="B49" s="20">
+        <v>46029.0</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E49" s="19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="G49" s="9">
-        <v>100.0</v>
+        <v>8</v>
+      </c>
+      <c r="G49" s="12">
+        <v>150.0</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="22" t="s">
-        <v>41</v>
+        <v>54</v>
+      </c>
+      <c r="B50" s="22">
+        <v>46029.0</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F50" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="12">
-        <v>50.0</v>
+        <v>6</v>
+      </c>
+      <c r="G50" s="9">
+        <v>125.0</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="20" t="s">
-        <v>41</v>
+        <v>50</v>
+      </c>
+      <c r="B51" s="20">
+        <v>46029.0</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G51" s="9">
-        <v>100.0</v>
+        <v>10</v>
+      </c>
+      <c r="G51" s="12">
+        <v>65.0</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="22" t="s">
-        <v>41</v>
+        <v>54</v>
+      </c>
+      <c r="B52" s="22">
+        <v>46029.0</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="E52" s="21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F52" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G52" s="12">
-        <v>50.0</v>
+        <v>12</v>
+      </c>
+      <c r="G52" s="9">
+        <v>28.0</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53" s="20" t="s">
-        <v>41</v>
+        <v>52</v>
+      </c>
+      <c r="B53" s="20">
+        <v>46029.0</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G53" s="9">
-        <v>50.0</v>
+        <v>4</v>
+      </c>
+      <c r="G53" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="B54" s="22" t="s">
-        <v>52</v>
+        <v>54</v>
+      </c>
+      <c r="B54" s="22">
+        <v>46029.0</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="E54" s="21" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F54" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54" s="12">
-        <v>75.0</v>
+        <v>14</v>
+      </c>
+      <c r="G54" s="9">
+        <v>90.0</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B55" s="20" t="s">
         <v>52</v>
       </c>
+      <c r="B55" s="20">
+        <v>46029.0</v>
+      </c>
       <c r="C55" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="E55" s="19" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="G55" s="9">
-        <v>150.0</v>
+        <v>13</v>
+      </c>
+      <c r="G55" s="12">
+        <v>50.0</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="B56" s="22" t="s">
         <v>52</v>
       </c>
+      <c r="B56" s="22">
+        <v>46029.0</v>
+      </c>
       <c r="C56" s="21" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="E56" s="21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F56" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" s="12">
-        <v>100.0</v>
+        <v>7</v>
+      </c>
+      <c r="G56" s="9">
+        <v>200.0</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B57" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B57" s="20">
+        <v>46029.0</v>
+      </c>
+      <c r="C57" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="19" t="s">
-        <v>57</v>
-      </c>
       <c r="D57" s="19" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G57" s="9">
-        <v>100.0</v>
+        <v>9</v>
+      </c>
+      <c r="G57" s="12">
+        <v>15.0</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="B58" s="22" t="s">
-        <v>56</v>
+        <v>52</v>
+      </c>
+      <c r="B58" s="22">
+        <v>46029.0</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="E58" s="21" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F58" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G58" s="12">
+        <v>13</v>
+      </c>
+      <c r="G58" s="9">
         <v>50.0</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B59" s="20" t="s">
-        <v>56</v>
+        <v>52</v>
+      </c>
+      <c r="B59" s="20">
+        <v>46029.0</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E59" s="19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F59" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="G59" s="9">
-        <v>50.0</v>
+      <c r="G59" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="B60" s="22" t="s">
-        <v>56</v>
+        <v>52</v>
+      </c>
+      <c r="B60" s="22">
+        <v>46029.0</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E60" s="21" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F60" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G60" s="12">
+        <v>6</v>
+      </c>
+      <c r="G60" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="19" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B61" s="20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="E61" s="19" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F61" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="G61" s="9">
+      <c r="G61" s="12">
         <v>100.0</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="21" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B62" s="22" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C62" s="21" t="s">
         <v>28</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="E62" s="21" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F62" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="G62" s="12">
+      <c r="G62" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C63" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B63" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="C63" s="19" t="s">
-        <v>30</v>
-      </c>
       <c r="D63" s="19" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G63" s="9">
-        <v>100.0</v>
+        <v>10</v>
+      </c>
+      <c r="G63" s="12">
+        <v>90.0</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="21" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B64" s="22" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D64" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E64" s="21" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F64" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G64" s="12">
-        <v>150.0</v>
+        <v>13</v>
+      </c>
+      <c r="G64" s="9">
+        <v>100.0</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="19" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B65" s="20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G65" s="9">
+        <v>13</v>
+      </c>
+      <c r="G65" s="12">
         <v>100.0</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="21" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B66" s="22" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="E66" s="21" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F66" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G66" s="12">
-        <v>100.0</v>
+        <v>13</v>
+      </c>
+      <c r="G66" s="9">
+        <v>85.0</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="19" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B67" s="20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="E67" s="19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G67" s="9">
-        <v>100.0</v>
+        <v>7</v>
+      </c>
+      <c r="G67" s="12">
+        <v>90.0</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="21" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B68" s="22" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="D68" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E68" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F68" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G68" s="12">
-        <v>200.0</v>
+      <c r="G68" s="9">
+        <v>160.0</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="19" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B69" s="20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="F69" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G69" s="9">
-        <v>53.0</v>
+        <v>13</v>
+      </c>
+      <c r="G69" s="12">
+        <v>30.0</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="21" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B70" s="22" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D70" s="21" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E70" s="21" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F70" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="G70" s="12">
-        <v>100.0</v>
+        <v>13</v>
+      </c>
+      <c r="G70" s="9">
+        <v>400.0</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="19" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B71" s="20" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E71" s="19" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G71" s="9">
-        <v>70.0</v>
+        <v>14</v>
+      </c>
+      <c r="G71" s="12">
+        <v>220.0</v>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="21" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B72" s="22" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C72" s="21" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="E72" s="21" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F72" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G72" s="12">
-        <v>60.0</v>
+        <v>6</v>
+      </c>
+      <c r="G72" s="9">
+        <v>100.0</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="19" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B73" s="20" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="E73" s="19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G73" s="9">
-        <v>200.0</v>
+        <v>6</v>
+      </c>
+      <c r="G73" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="21" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B74" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C74" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="D74" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E74" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="C74" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="D74" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="E74" s="21" t="s">
-        <v>10</v>
-      </c>
       <c r="F74" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="G74" s="12">
-        <v>150.0</v>
+        <v>13</v>
+      </c>
+      <c r="G74" s="9">
+        <v>40.0</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="19" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B75" s="20" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="E75" s="19" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="F75" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G75" s="9">
-        <v>55.0</v>
+        <v>9</v>
+      </c>
+      <c r="G75" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="21" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B76" s="22" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="D76" s="21" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E76" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F76" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G76" s="12">
-        <v>250.0</v>
+        <v>9</v>
+      </c>
+      <c r="G76" s="9">
+        <v>100.0</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="19" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="B77" s="20" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E77" s="19" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F77" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="G77" s="9">
+        <v>6</v>
+      </c>
+      <c r="G77" s="12">
         <v>100.0</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="21" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="B78" s="22" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="E78" s="21" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F78" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="G78" s="12">
+      <c r="G78" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="19" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="B79" s="20" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E79" s="19" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F79" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="G79" s="9">
-        <v>220.0</v>
+      <c r="G79" s="12">
+        <v>50.0</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="21" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="B80" s="22" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D80" s="21" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="E80" s="21" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F80" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="G80" s="12">
+      <c r="G80" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="19" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="B81" s="20" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F81" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="G81" s="9">
-        <v>100.0</v>
+      <c r="G81" s="12">
+        <v>50.0</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="21" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="B82" s="22" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="D82" s="21" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E82" s="21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F82" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="G82" s="12">
-        <v>85.0</v>
+      <c r="G82" s="9">
+        <v>50.0</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="19" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="B83" s="20" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D83" s="19" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F83" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G83" s="9">
-        <v>120.0</v>
+        <v>13</v>
+      </c>
+      <c r="G83" s="12">
+        <v>75.0</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="21" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B84" s="22" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C84" s="21" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="D84" s="21" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="E84" s="21" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F84" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G84" s="12">
-        <v>100.0</v>
+        <v>8</v>
+      </c>
+      <c r="G84" s="9">
+        <v>150.0</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="19" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B85" s="20" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D85" s="19" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E85" s="19" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F85" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="G85" s="9">
+        <v>13</v>
+      </c>
+      <c r="G85" s="12">
         <v>100.0</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="21" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B86" s="22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D86" s="21" t="s">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="E86" s="21" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F86" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="G86" s="12">
+      <c r="G86" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="19" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B87" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D87" s="19" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E87" s="19" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F87" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G87" s="9">
-        <v>100.0</v>
+        <v>6</v>
+      </c>
+      <c r="G87" s="12">
+        <v>50.0</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B88" s="22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C88" s="21" t="s">
         <v>25</v>
       </c>
       <c r="D88" s="21" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="E88" s="21" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F88" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="G88" s="12">
-        <v>100.0</v>
+        <v>6</v>
+      </c>
+      <c r="G88" s="9">
+        <v>50.0</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="19" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B89" s="20" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D89" s="19" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E89" s="19" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F89" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G89" s="9">
+        <v>10</v>
+      </c>
+      <c r="G89" s="12">
         <v>100.0</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="21" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B90" s="22" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="D90" s="21" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="E90" s="21" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F90" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="G90" s="12">
-        <v>90.0</v>
+        <v>10</v>
+      </c>
+      <c r="G90" s="9">
+        <v>100.0</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="19" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B91" s="20" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="D91" s="19" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E91" s="19" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="F91" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="G91" s="9">
-        <v>55.0</v>
+      <c r="G91" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="21" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="B92" s="22" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C92" s="21" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="D92" s="21" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="E92" s="21" t="s">
         <v>13</v>
@@ -2878,890 +2887,890 @@
       <c r="F92" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="G92" s="12">
-        <v>130.0</v>
+      <c r="G92" s="9">
+        <v>100.0</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="19" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B93" s="20" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D93" s="19" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E93" s="19" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F93" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G93" s="9">
-        <v>100.0</v>
+        <v>11</v>
+      </c>
+      <c r="G93" s="12">
+        <v>150.0</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="21" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="B94" s="22" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C94" s="21" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D94" s="21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E94" s="21" t="s">
         <v>13</v>
       </c>
       <c r="F94" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G94" s="12">
-        <v>90.0</v>
+        <v>11</v>
+      </c>
+      <c r="G94" s="9">
+        <v>100.0</v>
       </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="19" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="B95" s="20" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="D95" s="19" t="s">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="E95" s="19" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F95" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="G95" s="9">
-        <v>70.0</v>
+      <c r="G95" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="21" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B96" s="22" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="D96" s="21" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="E96" s="21" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F96" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G96" s="12">
-        <v>70.0</v>
+        <v>10</v>
+      </c>
+      <c r="G96" s="9">
+        <v>100.0</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="19" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="B97" s="20" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D97" s="19" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="E97" s="19" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F97" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G97" s="9">
-        <v>80.0</v>
+        <v>6</v>
+      </c>
+      <c r="G97" s="12">
+        <v>200.0</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="21" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="B98" s="22" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="D98" s="21" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="E98" s="21" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="F98" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G98" s="12">
-        <v>15.0</v>
+        <v>10</v>
+      </c>
+      <c r="G98" s="9">
+        <v>53.0</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="19" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="B99" s="20" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="D99" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E99" s="19" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F99" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G99" s="9">
+        <v>4</v>
+      </c>
+      <c r="G99" s="12">
         <v>100.0</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="21" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="B100" s="22" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D100" s="21" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E100" s="21" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="F100" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G100" s="12">
-        <v>40.0</v>
+        <v>7</v>
+      </c>
+      <c r="G100" s="9">
+        <v>70.0</v>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="19" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="B101" s="20" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C101" s="19" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D101" s="19" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="E101" s="19" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F101" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G101" s="9">
-        <v>100.0</v>
+        <v>10</v>
+      </c>
+      <c r="G101" s="12">
+        <v>60.0</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="21" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="B102" s="22" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D102" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E102" s="21" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F102" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="G102" s="12">
-        <v>100.0</v>
+        <v>13</v>
+      </c>
+      <c r="G102" s="9">
+        <v>200.0</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="19" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="B103" s="20" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D103" s="19" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E103" s="19" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F103" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G103" s="9">
-        <v>100.0</v>
+        <v>8</v>
+      </c>
+      <c r="G103" s="12">
+        <v>150.0</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="21" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="B104" s="22" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C104" s="21" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="D104" s="21" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="E104" s="21" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="F104" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G104" s="12">
-        <v>40.0</v>
+        <v>13</v>
+      </c>
+      <c r="G104" s="9">
+        <v>55.0</v>
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="19" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="B105" s="20" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D105" s="19" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="E105" s="19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F105" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G105" s="9">
-        <v>40.0</v>
+        <v>7</v>
+      </c>
+      <c r="G105" s="12">
+        <v>250.0</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="21" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="B106" s="22" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="C106" s="21" t="s">
-        <v>107</v>
+        <v>35</v>
       </c>
       <c r="D106" s="21" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E106" s="21" t="s">
         <v>15</v>
       </c>
       <c r="F106" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G106" s="12">
-        <v>200.0</v>
+        <v>5</v>
+      </c>
+      <c r="G106" s="9">
+        <v>100.0</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="19" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B107" s="20" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="D107" s="19" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E107" s="19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F107" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G107" s="9">
-        <v>60.0</v>
+        <v>5</v>
+      </c>
+      <c r="G107" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="21" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="B108" s="22" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="C108" s="21" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D108" s="21" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E108" s="21" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="F108" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="G108" s="12">
-        <v>65.0</v>
+      <c r="G108" s="9">
+        <v>220.0</v>
       </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="19" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="B109" s="20" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D109" s="19" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="E109" s="19" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F109" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G109" s="9">
+        <v>6</v>
+      </c>
+      <c r="G109" s="12">
         <v>100.0</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="21" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B110" s="22" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="C110" s="21" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="D110" s="21" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="E110" s="21" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F110" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G110" s="12">
+        <v>6</v>
+      </c>
+      <c r="G110" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="19" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="B111" s="20" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="D111" s="19" t="s">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="E111" s="19" t="s">
         <v>13</v>
       </c>
       <c r="F111" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G111" s="9">
-        <v>160.0</v>
+        <v>6</v>
+      </c>
+      <c r="G111" s="12">
+        <v>85.0</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="21" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="B112" s="22" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="C112" s="21" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="D112" s="21" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="E112" s="21" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F112" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="G112" s="12">
-        <v>70.0</v>
+      <c r="G112" s="9">
+        <v>120.0</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="19" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="B113" s="20" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="C113" s="19" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="D113" s="19" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="E113" s="19" t="s">
         <v>6</v>
       </c>
       <c r="F113" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="G113" s="9">
-        <v>150.0</v>
+        <v>14</v>
+      </c>
+      <c r="G113" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="21" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="B114" s="22" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="C114" s="21" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="D114" s="21" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E114" s="21" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F114" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G114" s="12">
+        <v>14</v>
+      </c>
+      <c r="G114" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="19" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="B115" s="20" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="C115" s="19" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="D115" s="19" t="s">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="E115" s="19" t="s">
         <v>9</v>
       </c>
       <c r="F115" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="G115" s="9">
-        <v>50.0</v>
+        <v>6</v>
+      </c>
+      <c r="G115" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="21" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B116" s="22" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="C116" s="21" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="D116" s="21" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E116" s="21" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F116" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G116" s="12">
+        <v>7</v>
+      </c>
+      <c r="G116" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="19" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="B117" s="20" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="D117" s="19" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="E117" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F117" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F117" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G117" s="9">
-        <v>150.0</v>
+      <c r="G117" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="21" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="B118" s="22" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="C118" s="21" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="D118" s="21" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E118" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F118" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="F118" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G118" s="12">
+      <c r="G118" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="19" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="B119" s="20" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="D119" s="19" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="E119" s="19" t="s">
         <v>5</v>
       </c>
       <c r="F119" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G119" s="9">
-        <v>55.0</v>
+        <v>9</v>
+      </c>
+      <c r="G119" s="12">
+        <v>90.0</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="21" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="B120" s="22" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C120" s="21" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="D120" s="21" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="E120" s="21" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="F120" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G120" s="12">
-        <v>75.0</v>
+        <v>13</v>
+      </c>
+      <c r="G120" s="9">
+        <v>55.0</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="19" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="B121" s="20" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C121" s="19" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="D121" s="19" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E121" s="19" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F121" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="G121" s="9">
-        <v>20.0</v>
+        <v>6</v>
+      </c>
+      <c r="G121" s="12">
+        <v>130.0</v>
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="21" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B122" s="22" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C122" s="21" t="s">
-        <v>28</v>
+        <v>102</v>
       </c>
       <c r="D122" s="21" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E122" s="21" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F122" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="G122" s="12">
-        <v>150.0</v>
+        <v>13</v>
+      </c>
+      <c r="G122" s="9">
+        <v>100.0</v>
       </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="19" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="B123" s="20" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C123" s="19" t="s">
-        <v>28</v>
+        <v>106</v>
       </c>
       <c r="D123" s="19" t="s">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="E123" s="19" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F123" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G123" s="9">
-        <v>100.0</v>
+        <v>6</v>
+      </c>
+      <c r="G123" s="12">
+        <v>90.0</v>
       </c>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="21" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="B124" s="22" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="C124" s="21" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D124" s="21" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E124" s="21" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F124" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G124" s="12">
-        <v>150.0</v>
+        <v>6</v>
+      </c>
+      <c r="G124" s="9">
+        <v>70.0</v>
       </c>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="19" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="B125" s="20" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="C125" s="19" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D125" s="19" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E125" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F125" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G125" s="9">
-        <v>60.0</v>
+        <v>6</v>
+      </c>
+      <c r="G125" s="12">
+        <v>70.0</v>
       </c>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="21" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="B126" s="22" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="C126" s="21" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D126" s="21" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="E126" s="21" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F126" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G126" s="12">
-        <v>200.0</v>
+        <v>7</v>
+      </c>
+      <c r="G126" s="9">
+        <v>80.0</v>
       </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="19" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B127" s="20" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="C127" s="19" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="D127" s="19" t="s">
         <v>30</v>
       </c>
       <c r="E127" s="19" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="F127" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="G127" s="9">
-        <v>100.0</v>
+        <v>5</v>
+      </c>
+      <c r="G127" s="12">
+        <v>15.0</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="21" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="B128" s="22" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="C128" s="21" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="D128" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E128" s="21" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F128" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G128" s="12">
+        <v>10</v>
+      </c>
+      <c r="G128" s="9">
         <v>100.0</v>
       </c>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="19" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B129" s="20" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="C129" s="19" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="D129" s="19" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E129" s="19" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="F129" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="G129" s="9">
-        <v>100.0</v>
+        <v>6</v>
+      </c>
+      <c r="G129" s="12">
+        <v>40.0</v>
       </c>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="21" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B130" s="22" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="C130" s="21" t="s">
-        <v>128</v>
+        <v>36</v>
       </c>
       <c r="D130" s="21" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="E130" s="21" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F130" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G130" s="12">
-        <v>50.0</v>
+        <v>13</v>
+      </c>
+      <c r="G130" s="9">
+        <v>100.0</v>
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="19" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="B131" s="20" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="C131" s="19" t="s">
         <v>28</v>
@@ -3770,186 +3779,824 @@
         <v>28</v>
       </c>
       <c r="E131" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F131" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G131" s="9">
-        <v>270.0</v>
+        <v>6</v>
+      </c>
+      <c r="G131" s="12">
+        <v>100.0</v>
       </c>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="21" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="B132" s="22" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="C132" s="21" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D132" s="21" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E132" s="21" t="s">
         <v>4</v>
       </c>
       <c r="F132" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="G132" s="12">
-        <v>30.0</v>
+        <v>6</v>
+      </c>
+      <c r="G132" s="9">
+        <v>100.0</v>
       </c>
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="19" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="B133" s="20" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="C133" s="19" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D133" s="19" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E133" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F133" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G133" s="9">
-        <v>150.0</v>
+        <v>11</v>
+      </c>
+      <c r="G133" s="12">
+        <v>40.0</v>
       </c>
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="21" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="B134" s="22" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C134" s="21" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D134" s="21" t="s">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c r="E134" s="21" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F134" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G134" s="12">
-        <v>100.0</v>
+        <v>11</v>
+      </c>
+      <c r="G134" s="9">
+        <v>40.0</v>
       </c>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="B135" s="20">
-        <v>46362.0</v>
+        <v>115</v>
+      </c>
+      <c r="B135" s="20" t="s">
+        <v>116</v>
       </c>
       <c r="C135" s="19" t="s">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="D135" s="19" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E135" s="19" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F135" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="G135" s="9">
-        <v>230.0</v>
+      <c r="G135" s="12">
+        <v>200.0</v>
       </c>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B136" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C136" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D136" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E136" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F136" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G136" s="9">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="137" ht="15.75" customHeight="1">
+      <c r="A137" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B137" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C137" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D137" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E137" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F137" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G137" s="12">
+        <v>65.0</v>
+      </c>
+    </row>
+    <row r="138" ht="15.75" customHeight="1">
+      <c r="A138" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="B138" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="C138" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D138" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="E138" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F138" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G138" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="139" ht="15.75" customHeight="1">
+      <c r="A139" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="B139" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C139" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D139" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="E139" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F139" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G139" s="12">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="140" ht="15.75" customHeight="1">
+      <c r="A140" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="B140" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="C140" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="D140" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="E140" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F140" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G140" s="9">
+        <v>160.0</v>
+      </c>
+    </row>
+    <row r="141" ht="15.75" customHeight="1">
+      <c r="A141" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B141" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C141" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D141" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="E141" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F141" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G141" s="12">
+        <v>70.0</v>
+      </c>
+    </row>
+    <row r="142" ht="15.75" customHeight="1">
+      <c r="A142" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B142" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C142" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="D142" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E142" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F142" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="G142" s="9">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="143" ht="15.75" customHeight="1">
+      <c r="A143" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="B143" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C143" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D143" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="E143" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F143" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G143" s="12">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="144" ht="15.75" customHeight="1">
+      <c r="A144" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B144" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C144" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D144" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="E144" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F144" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="G144" s="9">
+        <v>50.0</v>
+      </c>
+    </row>
+    <row r="145" ht="15.75" customHeight="1">
+      <c r="A145" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B145" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C145" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D145" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E145" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F145" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G145" s="12">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="146" ht="15.75" customHeight="1">
+      <c r="A146" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B146" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C146" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="D146" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E146" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F146" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G146" s="9">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="147" ht="15.75" customHeight="1">
+      <c r="A147" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B147" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C147" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D147" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E147" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F147" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G147" s="12">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="148" ht="15.75" customHeight="1">
+      <c r="A148" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="B148" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="C148" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D148" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="E148" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="F148" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G148" s="9">
+        <v>55.0</v>
+      </c>
+    </row>
+    <row r="149" ht="15.75" customHeight="1">
+      <c r="A149" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="B149" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C149" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D149" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E149" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F149" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G149" s="12">
+        <v>75.0</v>
+      </c>
+    </row>
+    <row r="150" ht="15.75" customHeight="1">
+      <c r="A150" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="B150" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="C150" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="D150" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="E150" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F150" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="G150" s="9">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="151" ht="15.75" customHeight="1">
+      <c r="A151" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B151" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C151" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D151" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E151" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F151" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="G151" s="12">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="152" ht="15.75" customHeight="1">
+      <c r="A152" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="B152" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="C152" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D152" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="E152" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F152" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G152" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="153" ht="15.75" customHeight="1">
+      <c r="A153" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="B153" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C153" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D153" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E153" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F153" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G153" s="12">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="154" ht="15.75" customHeight="1">
+      <c r="A154" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B154" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="C154" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D154" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E154" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F154" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G154" s="9">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="155" ht="15.75" customHeight="1">
+      <c r="A155" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="B155" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C155" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D155" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E155" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F155" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G155" s="12">
+        <v>200.0</v>
+      </c>
+    </row>
+    <row r="156" ht="15.75" customHeight="1">
+      <c r="A156" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B156" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="C156" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D156" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E156" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F156" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="G156" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="157" ht="15.75" customHeight="1">
+      <c r="A157" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="B157" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C157" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D157" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E157" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F157" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G157" s="12">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="158" ht="15.75" customHeight="1">
+      <c r="A158" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B158" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="C158" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="D158" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E158" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="F158" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="G158" s="9">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="159" ht="15.75" customHeight="1">
+      <c r="A159" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B159" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B136" s="22">
+      <c r="C159" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="D159" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E159" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F159" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G159" s="12">
+        <v>50.0</v>
+      </c>
+    </row>
+    <row r="160" ht="15.75" customHeight="1">
+      <c r="A160" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="B160" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="C160" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D160" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E160" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F160" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G160" s="9">
+        <v>270.0</v>
+      </c>
+    </row>
+    <row r="161" ht="15.75" customHeight="1">
+      <c r="A161" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="B161" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="C161" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D161" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="E161" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F161" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G161" s="12">
+        <v>30.0</v>
+      </c>
+    </row>
+    <row r="162" ht="15.75" customHeight="1">
+      <c r="A162" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="B162" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="C162" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D162" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E162" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F162" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G162" s="9">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="163" ht="15.75" customHeight="1">
+      <c r="A163" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="B163" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C163" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D163" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="E163" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F163" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G163" s="12">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="164" ht="15.75" customHeight="1">
+      <c r="A164" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="B164" s="22">
         <v>46362.0</v>
       </c>
-      <c r="C136" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D136" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="E136" s="21" t="s">
+      <c r="C164" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D164" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E164" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F164" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G164" s="9">
+        <v>230.0</v>
+      </c>
+    </row>
+    <row r="165" ht="15.75" customHeight="1">
+      <c r="A165" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="B165" s="20">
+        <v>46362.0</v>
+      </c>
+      <c r="C165" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D165" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="E165" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="F136" s="21" t="s">
+      <c r="F165" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G136" s="12">
+      <c r="G165" s="12">
         <v>80.0</v>
       </c>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="19"/>
-      <c r="B137" s="20"/>
-      <c r="C137" s="19"/>
-      <c r="D137" s="19"/>
-      <c r="E137" s="19"/>
-      <c r="F137" s="19"/>
-      <c r="G137" s="9"/>
-    </row>
-    <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="21"/>
-      <c r="B138" s="22"/>
-      <c r="C138" s="21"/>
-      <c r="D138" s="21"/>
-      <c r="E138" s="21"/>
-      <c r="F138" s="21"/>
-      <c r="G138" s="12"/>
-    </row>
-    <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="19"/>
-      <c r="B139" s="20"/>
-      <c r="C139" s="19"/>
-      <c r="D139" s="19"/>
-      <c r="E139" s="19"/>
-      <c r="F139" s="19"/>
-      <c r="G139" s="9"/>
-    </row>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1">
+      <c r="A166" s="21"/>
+      <c r="B166" s="22"/>
+      <c r="C166" s="21"/>
+      <c r="D166" s="21"/>
+      <c r="E166" s="21"/>
+      <c r="F166" s="21"/>
+      <c r="G166" s="9"/>
+    </row>
+    <row r="167" ht="15.75" customHeight="1">
+      <c r="A167" s="19"/>
+      <c r="B167" s="20"/>
+      <c r="C167" s="19"/>
+      <c r="D167" s="19"/>
+      <c r="E167" s="19"/>
+      <c r="F167" s="19"/>
+      <c r="G167" s="12"/>
+    </row>
+    <row r="168" ht="15.75" customHeight="1">
+      <c r="A168" s="21"/>
+      <c r="B168" s="22"/>
+      <c r="C168" s="21"/>
+      <c r="D168" s="21"/>
+      <c r="E168" s="21"/>
+      <c r="F168" s="21"/>
+      <c r="G168" s="9"/>
+    </row>
     <row r="169" ht="15.75" customHeight="1"/>
     <row r="170" ht="15.75" customHeight="1"/>
     <row r="171" ht="15.75" customHeight="1"/>
@@ -4851,7 +5498,6 @@
     <row r="1067" ht="15.75" customHeight="1"/>
     <row r="1068" ht="15.75" customHeight="1"/>
     <row r="1069" ht="15.75" customHeight="1"/>
-    <row r="1070" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
